--- a/research/traditional_assets/database/data/switzerland/switzerland_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_paper_forest_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07460628441596914</v>
+        <v>0.07453578924072182</v>
       </c>
       <c r="C2">
-        <v>518.6105162228627</v>
+        <v>514.5387657210608</v>
       </c>
       <c r="D2">
-        <v>485.3105162228626</v>
+        <v>486.5010890518844</v>
       </c>
       <c r="E2">
-        <v>-40.63233308234578</v>
+        <v>-35.37000975152232</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.262323330823458</v>
       </c>
       <c r="G2">
         <v>33.3</v>
@@ -1451,28 +1451,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2646948635404199</v>
       </c>
       <c r="N2">
-        <v>50.55000000000001</v>
+        <v>50.28530513645959</v>
       </c>
       <c r="O2">
-        <v>7.380300000000001</v>
+        <v>7.3416545499231</v>
       </c>
       <c r="P2">
-        <v>43.16970000000001</v>
+        <v>42.94365058653649</v>
       </c>
       <c r="Q2">
-        <v>65.96970000000002</v>
+        <v>65.74365058653649</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07460628441596914</v>
+        <v>0.07485477499062811</v>
       </c>
       <c r="T2">
-        <v>0.6652721574126822</v>
+        <v>0.6710109697604643</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>190.9746162954191</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07453578924072182</v>
+        <v>0.0744652940654745</v>
       </c>
       <c r="C3">
-        <v>514.5387657210608</v>
+        <v>510.4728710559399</v>
       </c>
       <c r="D3">
-        <v>486.5010890518844</v>
+        <v>487.6975177175868</v>
       </c>
       <c r="E3">
-        <v>-35.37000975152232</v>
+        <v>-30.10768642069887</v>
       </c>
       <c r="F3">
-        <v>5.262323330823458</v>
+        <v>10.52464666164692</v>
       </c>
       <c r="G3">
         <v>33.3</v>
@@ -1533,28 +1533,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M3">
-        <v>0.2646948635404199</v>
+        <v>0.5293897270808399</v>
       </c>
       <c r="N3">
-        <v>50.28530513645959</v>
+        <v>50.02061027291917</v>
       </c>
       <c r="O3">
-        <v>7.3416545499231</v>
+        <v>7.303009099846198</v>
       </c>
       <c r="P3">
-        <v>42.94365058653649</v>
+        <v>42.71760117307297</v>
       </c>
       <c r="Q3">
-        <v>65.74365058653649</v>
+        <v>65.51760117307298</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07485477499062811</v>
+        <v>0.0751083368015046</v>
       </c>
       <c r="T3">
-        <v>0.6710109697604643</v>
+        <v>0.6768669007275889</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>190.9746162954191</v>
+        <v>95.48730814770954</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0744652940654745</v>
+        <v>0.07439479889022718</v>
       </c>
       <c r="C4">
-        <v>510.4728710559399</v>
+        <v>506.4128755369388</v>
       </c>
       <c r="D4">
-        <v>487.6975177175868</v>
+        <v>488.8998455294091</v>
       </c>
       <c r="E4">
-        <v>-30.10768642069887</v>
+        <v>-24.84536308987541</v>
       </c>
       <c r="F4">
-        <v>10.52464666164692</v>
+        <v>15.78696999247037</v>
       </c>
       <c r="G4">
         <v>33.3</v>
@@ -1615,28 +1615,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M4">
-        <v>0.5293897270808399</v>
+        <v>0.7940845906212598</v>
       </c>
       <c r="N4">
-        <v>50.02061027291917</v>
+        <v>49.75591540937875</v>
       </c>
       <c r="O4">
-        <v>7.303009099846198</v>
+        <v>7.264363649769297</v>
       </c>
       <c r="P4">
-        <v>42.71760117307297</v>
+        <v>42.49155175960945</v>
       </c>
       <c r="Q4">
-        <v>65.51760117307298</v>
+        <v>65.29155175960945</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0751083368015046</v>
+        <v>0.07536712669095587</v>
       </c>
       <c r="T4">
-        <v>0.6768669007275889</v>
+        <v>0.6828435725393964</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>95.48730814770954</v>
+        <v>63.65820543180636</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07439479889022718</v>
+        <v>0.07432430371497989</v>
       </c>
       <c r="C5">
-        <v>506.4128755369388</v>
+        <v>502.3588229016369</v>
       </c>
       <c r="D5">
-        <v>488.8998455294091</v>
+        <v>490.1081162249308</v>
       </c>
       <c r="E5">
-        <v>-24.84536308987541</v>
+        <v>-19.58303975905195</v>
       </c>
       <c r="F5">
-        <v>15.78696999247037</v>
+        <v>21.04929332329383</v>
       </c>
       <c r="G5">
         <v>33.3</v>
@@ -1697,28 +1697,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M5">
-        <v>0.7940845906212598</v>
+        <v>1.05877945416168</v>
       </c>
       <c r="N5">
-        <v>49.75591540937875</v>
+        <v>49.49122054583833</v>
       </c>
       <c r="O5">
-        <v>7.264363649769297</v>
+        <v>7.225718199692396</v>
       </c>
       <c r="P5">
-        <v>42.49155175960945</v>
+        <v>42.26550234614594</v>
       </c>
       <c r="Q5">
-        <v>65.29155175960945</v>
+        <v>65.06550234614593</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07536712669095587</v>
+        <v>0.07563130803643738</v>
       </c>
       <c r="T5">
-        <v>0.6828435725393964</v>
+        <v>0.6889447583472834</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.65820543180636</v>
+        <v>47.74365407385477</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07432430371497989</v>
+        <v>0.07425380853973255</v>
       </c>
       <c r="C6">
-        <v>502.3588229016369</v>
+        <v>498.3107573210606</v>
       </c>
       <c r="D6">
-        <v>490.1081162249308</v>
+        <v>491.3223739751779</v>
       </c>
       <c r="E6">
-        <v>-19.58303975905195</v>
+        <v>-14.32071642822849</v>
       </c>
       <c r="F6">
-        <v>21.04929332329383</v>
+        <v>26.31161665411729</v>
       </c>
       <c r="G6">
         <v>33.3</v>
@@ -1779,28 +1779,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M6">
-        <v>1.05877945416168</v>
+        <v>1.3234743177021</v>
       </c>
       <c r="N6">
-        <v>49.49122054583833</v>
+        <v>49.22652568229791</v>
       </c>
       <c r="O6">
-        <v>7.225718199692396</v>
+        <v>7.187072749615495</v>
       </c>
       <c r="P6">
-        <v>42.26550234614594</v>
+        <v>42.03945293268242</v>
       </c>
       <c r="Q6">
-        <v>65.06550234614593</v>
+        <v>64.83945293268242</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07563130803643738</v>
+        <v>0.07590105109445533</v>
       </c>
       <c r="T6">
-        <v>0.6889447583472834</v>
+        <v>0.6951743901721785</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.74365407385477</v>
+        <v>38.19492325908382</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07425380853973255</v>
+        <v>0.07418331336448525</v>
       </c>
       <c r="C7">
-        <v>498.3107573210606</v>
+        <v>494.2687234050607</v>
       </c>
       <c r="D7">
-        <v>491.3223739751779</v>
+        <v>492.5426633900015</v>
       </c>
       <c r="E7">
-        <v>-14.32071642822849</v>
+        <v>-9.05839309740503</v>
       </c>
       <c r="F7">
-        <v>26.31161665411729</v>
+        <v>31.57393998494075</v>
       </c>
       <c r="G7">
         <v>33.3</v>
@@ -1861,28 +1861,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M7">
-        <v>1.3234743177021</v>
+        <v>1.58816918124252</v>
       </c>
       <c r="N7">
-        <v>49.22652568229791</v>
+        <v>48.96183081875749</v>
       </c>
       <c r="O7">
-        <v>7.187072749615495</v>
+        <v>7.148427299538593</v>
       </c>
       <c r="P7">
-        <v>42.03945293268242</v>
+        <v>41.81340351921889</v>
       </c>
       <c r="Q7">
-        <v>64.83945293268242</v>
+        <v>64.61340351921889</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07590105109445533</v>
+        <v>0.07617653336647368</v>
       </c>
       <c r="T7">
-        <v>0.6951743901721785</v>
+        <v>0.7015365673550501</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.19492325908382</v>
+        <v>31.82910271590318</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07418331336448525</v>
+        <v>0.07411281818923796</v>
       </c>
       <c r="C8">
-        <v>494.2687234050607</v>
+        <v>490.2327662077805</v>
       </c>
       <c r="D8">
-        <v>492.5426633900015</v>
+        <v>493.7690295235447</v>
       </c>
       <c r="E8">
-        <v>-9.058393097405034</v>
+        <v>-3.796069766581581</v>
       </c>
       <c r="F8">
-        <v>31.57393998494075</v>
+        <v>36.8362633157642</v>
       </c>
       <c r="G8">
         <v>33.3</v>
@@ -1943,28 +1943,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M8">
-        <v>1.58816918124252</v>
+        <v>1.852864044782939</v>
       </c>
       <c r="N8">
-        <v>48.96183081875749</v>
+        <v>48.69713595521707</v>
       </c>
       <c r="O8">
-        <v>7.148427299538593</v>
+        <v>7.109781849461692</v>
       </c>
       <c r="P8">
-        <v>41.81340351921889</v>
+        <v>41.58735410575538</v>
       </c>
       <c r="Q8">
-        <v>64.61340351921889</v>
+        <v>64.38735410575538</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07617653336647368</v>
+        <v>0.0764579399884279</v>
       </c>
       <c r="T8">
-        <v>0.7015365673550501</v>
+        <v>0.7080355655526072</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.82910271590318</v>
+        <v>27.28208804220273</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07411281818923794</v>
+        <v>0.07404232301399062</v>
       </c>
       <c r="C9">
-        <v>490.2327662077807</v>
+        <v>486.202931233199</v>
       </c>
       <c r="D9">
-        <v>493.7690295235449</v>
+        <v>495.0015178797867</v>
       </c>
       <c r="E9">
-        <v>-3.796069766581574</v>
+        <v>1.466253564241882</v>
       </c>
       <c r="F9">
-        <v>36.83626331576421</v>
+        <v>42.09858664658766</v>
       </c>
       <c r="G9">
         <v>33.3</v>
@@ -2025,28 +2025,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M9">
-        <v>1.852864044782939</v>
+        <v>2.117558908323359</v>
       </c>
       <c r="N9">
-        <v>48.69713595521707</v>
+        <v>48.43244109167665</v>
       </c>
       <c r="O9">
-        <v>7.109781849461692</v>
+        <v>7.07113639938479</v>
       </c>
       <c r="P9">
-        <v>41.58735410575538</v>
+        <v>41.36130469229186</v>
       </c>
       <c r="Q9">
-        <v>64.38735410575538</v>
+        <v>64.16130469229186</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0764579399884279</v>
+        <v>0.07674546414564198</v>
       </c>
       <c r="T9">
-        <v>0.7080355655526072</v>
+        <v>0.7146758463196762</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.28208804220273</v>
+        <v>23.87182703692739</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07404232301399062</v>
+        <v>0.07397182783874331</v>
       </c>
       <c r="C10">
-        <v>486.202931233199</v>
+        <v>482.179264440757</v>
       </c>
       <c r="D10">
-        <v>495.0015178797867</v>
+        <v>496.2401744181682</v>
       </c>
       <c r="E10">
-        <v>1.466253564241882</v>
+        <v>6.728576895065338</v>
       </c>
       <c r="F10">
-        <v>42.09858664658766</v>
+        <v>47.36090997741112</v>
       </c>
       <c r="G10">
         <v>33.3</v>
@@ -2107,28 +2107,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M10">
-        <v>2.117558908323359</v>
+        <v>2.382253771863779</v>
       </c>
       <c r="N10">
-        <v>48.43244109167665</v>
+        <v>48.16774622813623</v>
       </c>
       <c r="O10">
-        <v>7.07113639938479</v>
+        <v>7.032490949307889</v>
       </c>
       <c r="P10">
-        <v>41.36130469229186</v>
+        <v>41.13525527882834</v>
       </c>
       <c r="Q10">
-        <v>64.16130469229186</v>
+        <v>63.93525527882834</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07674546414564198</v>
+        <v>0.07703930751510253</v>
       </c>
       <c r="T10">
-        <v>0.7146758463196762</v>
+        <v>0.721462067323384</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.87182703692739</v>
+        <v>21.21940181060212</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07397182783874331</v>
+        <v>0.07390133266349599</v>
       </c>
       <c r="C11">
-        <v>482.179264440757</v>
+        <v>478.1618122510738</v>
       </c>
       <c r="D11">
-        <v>496.2401744181682</v>
+        <v>497.4850455593084</v>
       </c>
       <c r="E11">
-        <v>6.728576895065338</v>
+        <v>11.99090022588879</v>
       </c>
       <c r="F11">
-        <v>47.36090997741112</v>
+        <v>52.62323330823457</v>
       </c>
       <c r="G11">
         <v>33.3</v>
@@ -2189,28 +2189,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M11">
-        <v>2.382253771863779</v>
+        <v>2.646948635404199</v>
       </c>
       <c r="N11">
-        <v>48.16774622813623</v>
+        <v>47.90305136459581</v>
       </c>
       <c r="O11">
-        <v>7.032490949307889</v>
+        <v>6.993845499230988</v>
       </c>
       <c r="P11">
-        <v>41.13525527882834</v>
+        <v>40.90920586536483</v>
       </c>
       <c r="Q11">
-        <v>63.93525527882834</v>
+        <v>63.70920586536482</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07703930751510253</v>
+        <v>0.07733968073721777</v>
       </c>
       <c r="T11">
-        <v>0.721462067323384</v>
+        <v>0.7283990932382856</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.21940181060212</v>
+        <v>19.09746162954191</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07390133266349599</v>
+        <v>0.07383083748824867</v>
       </c>
       <c r="C12">
-        <v>478.1618122510738</v>
+        <v>474.1506215517433</v>
       </c>
       <c r="D12">
-        <v>497.4850455593084</v>
+        <v>498.7361781908014</v>
       </c>
       <c r="E12">
-        <v>11.9909002258888</v>
+        <v>17.25322355671226</v>
       </c>
       <c r="F12">
-        <v>52.62323330823458</v>
+        <v>57.88555663905804</v>
       </c>
       <c r="G12">
         <v>33.3</v>
@@ -2271,28 +2271,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M12">
-        <v>2.646948635404199</v>
+        <v>2.911643498944619</v>
       </c>
       <c r="N12">
-        <v>47.90305136459581</v>
+        <v>47.63835650105539</v>
       </c>
       <c r="O12">
-        <v>6.993845499230988</v>
+        <v>6.955200049154087</v>
       </c>
       <c r="P12">
-        <v>40.90920586536483</v>
+        <v>40.6831564519013</v>
       </c>
       <c r="Q12">
-        <v>63.70920586536482</v>
+        <v>63.48315645190131</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07733968073721777</v>
+        <v>0.07764680391938053</v>
       </c>
       <c r="T12">
-        <v>0.7283990932382856</v>
+        <v>0.7354920073759939</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.09746162954191</v>
+        <v>17.36132875412901</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07383083748824867</v>
+        <v>0.07376034231300137</v>
       </c>
       <c r="C13">
-        <v>474.1506215517433</v>
+        <v>470.1457397032219</v>
       </c>
       <c r="D13">
-        <v>498.7361781908014</v>
+        <v>499.9936196731035</v>
       </c>
       <c r="E13">
-        <v>17.25322355671226</v>
+        <v>22.51554688753571</v>
       </c>
       <c r="F13">
-        <v>57.88555663905804</v>
+        <v>63.14787996988149</v>
       </c>
       <c r="G13">
         <v>33.3</v>
@@ -2353,28 +2353,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M13">
-        <v>2.911643498944619</v>
+        <v>3.176338362485039</v>
       </c>
       <c r="N13">
-        <v>47.63835650105539</v>
+        <v>47.37366163751497</v>
       </c>
       <c r="O13">
-        <v>6.955200049154087</v>
+        <v>6.916554599077186</v>
       </c>
       <c r="P13">
-        <v>40.6831564519013</v>
+        <v>40.45710703843778</v>
       </c>
       <c r="Q13">
-        <v>63.48315645190131</v>
+        <v>63.25710703843778</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07764680391938053</v>
+        <v>0.07796090717386518</v>
       </c>
       <c r="T13">
-        <v>0.7354920073759939</v>
+        <v>0.7427461241077409</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.36132875412901</v>
+        <v>15.91455135795159</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07376034231300137</v>
+        <v>0.07368984713775403</v>
       </c>
       <c r="C14">
-        <v>470.1457397032219</v>
+        <v>466.1472145448055</v>
       </c>
       <c r="D14">
-        <v>499.9936196731035</v>
+        <v>501.2574178455105</v>
       </c>
       <c r="E14">
-        <v>22.51554688753571</v>
+        <v>27.77787021835917</v>
       </c>
       <c r="F14">
-        <v>63.14787996988149</v>
+        <v>68.41020330070495</v>
       </c>
       <c r="G14">
         <v>33.3</v>
@@ -2435,28 +2435,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M14">
-        <v>3.176338362485039</v>
+        <v>3.441033226025459</v>
       </c>
       <c r="N14">
-        <v>47.37366163751497</v>
+        <v>47.10896677397455</v>
       </c>
       <c r="O14">
-        <v>6.916554599077186</v>
+        <v>6.877909149000284</v>
       </c>
       <c r="P14">
-        <v>40.45710703843778</v>
+        <v>40.23105762497427</v>
       </c>
       <c r="Q14">
-        <v>63.25710703843778</v>
+        <v>63.03105762497427</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07796090717386518</v>
+        <v>0.07828223119282074</v>
       </c>
       <c r="T14">
-        <v>0.7427461241077409</v>
+        <v>0.7501670021436661</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.91455135795159</v>
+        <v>14.69035509964762</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07368984713775403</v>
+        <v>0.07361935196250674</v>
       </c>
       <c r="C15">
-        <v>466.1472145448055</v>
+        <v>462.1550944006935</v>
       </c>
       <c r="D15">
-        <v>501.2574178455105</v>
+        <v>502.527621032222</v>
       </c>
       <c r="E15">
-        <v>27.77787021835917</v>
+        <v>33.04019354918263</v>
       </c>
       <c r="F15">
-        <v>68.41020330070495</v>
+        <v>73.67252663152841</v>
       </c>
       <c r="G15">
         <v>33.3</v>
@@ -2517,28 +2517,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M15">
-        <v>3.441033226025459</v>
+        <v>3.705728089565879</v>
       </c>
       <c r="N15">
-        <v>47.10896677397455</v>
+        <v>46.84427191043413</v>
       </c>
       <c r="O15">
-        <v>6.877909149000284</v>
+        <v>6.839263698923383</v>
       </c>
       <c r="P15">
-        <v>40.23105762497427</v>
+        <v>40.00500821151075</v>
       </c>
       <c r="Q15">
-        <v>63.03105762497427</v>
+        <v>62.80500821151075</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07828223119282074</v>
+        <v>0.07861102786337992</v>
       </c>
       <c r="T15">
-        <v>0.7501670021436661</v>
+        <v>0.7577604587385662</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.69035509964762</v>
+        <v>13.64104402110136</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07361935196250674</v>
+        <v>0.07374100678725941</v>
       </c>
       <c r="C16">
-        <v>462.1550944006935</v>
+        <v>454.7047715415952</v>
       </c>
       <c r="D16">
-        <v>502.527621032222</v>
+        <v>500.3396215039471</v>
       </c>
       <c r="E16">
-        <v>33.04019354918263</v>
+        <v>38.3025168800061</v>
       </c>
       <c r="F16">
-        <v>73.67252663152841</v>
+        <v>78.93484996235188</v>
       </c>
       <c r="G16">
         <v>33.3</v>
@@ -2599,45 +2599,45 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M16">
-        <v>3.705728089565879</v>
+        <v>4.088825228049827</v>
       </c>
       <c r="N16">
-        <v>46.84427191043413</v>
+        <v>46.46117477195018</v>
       </c>
       <c r="O16">
-        <v>6.839263698923383</v>
+        <v>6.783331516704727</v>
       </c>
       <c r="P16">
-        <v>40.00500821151075</v>
+        <v>39.67784325524546</v>
       </c>
       <c r="Q16">
-        <v>62.80500821151075</v>
+        <v>62.47784325524546</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07861102786337992</v>
+        <v>0.07894756092618754</v>
       </c>
       <c r="T16">
-        <v>0.7577604587385662</v>
+        <v>0.7655325849004053</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.146</v>
       </c>
       <c r="W16">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.64104402110136</v>
+        <v>12.3629642209261</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07374100678725941</v>
+        <v>0.07368332161201209</v>
       </c>
       <c r="C17">
-        <v>454.7047715415952</v>
+        <v>450.4775536817497</v>
       </c>
       <c r="D17">
-        <v>500.3396215039471</v>
+        <v>501.374726974925</v>
       </c>
       <c r="E17">
-        <v>38.30251688000608</v>
+        <v>43.56484021082954</v>
       </c>
       <c r="F17">
-        <v>78.93484996235186</v>
+        <v>84.19717329317533</v>
       </c>
       <c r="G17">
         <v>33.3</v>
@@ -2681,28 +2681,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M17">
-        <v>4.088825228049826</v>
+        <v>4.361413576586481</v>
       </c>
       <c r="N17">
-        <v>46.46117477195018</v>
+        <v>46.18858642341353</v>
       </c>
       <c r="O17">
-        <v>6.783331516704727</v>
+        <v>6.743533617818375</v>
       </c>
       <c r="P17">
-        <v>39.67784325524546</v>
+        <v>39.44505280559515</v>
       </c>
       <c r="Q17">
-        <v>62.47784325524546</v>
+        <v>62.24505280559515</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07894756092618754</v>
+        <v>0.07929210668096678</v>
       </c>
       <c r="T17">
-        <v>0.7655325849004053</v>
+        <v>0.7734897616851452</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.3629642209261</v>
+        <v>11.59027895711822</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07368332161201209</v>
+        <v>0.07362563643676479</v>
       </c>
       <c r="C18">
-        <v>450.4775536817497</v>
+        <v>446.2546275649252</v>
       </c>
       <c r="D18">
-        <v>501.374726974925</v>
+        <v>502.4141241889239</v>
       </c>
       <c r="E18">
-        <v>43.56484021082954</v>
+        <v>48.82716354165301</v>
       </c>
       <c r="F18">
-        <v>84.19717329317533</v>
+        <v>89.45949662399879</v>
       </c>
       <c r="G18">
         <v>33.3</v>
@@ -2763,28 +2763,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M18">
-        <v>4.361413576586481</v>
+        <v>4.634001925123137</v>
       </c>
       <c r="N18">
-        <v>46.18858642341353</v>
+        <v>45.91599807487687</v>
       </c>
       <c r="O18">
-        <v>6.743533617818375</v>
+        <v>6.703735718932023</v>
       </c>
       <c r="P18">
-        <v>39.44505280559515</v>
+        <v>39.21226235594485</v>
       </c>
       <c r="Q18">
-        <v>62.24505280559515</v>
+        <v>62.01226235594486</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07929210668096678</v>
+        <v>0.07964495474309011</v>
       </c>
       <c r="T18">
-        <v>0.7734897616851452</v>
+        <v>0.7816386776695173</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.59027895711822</v>
+        <v>10.90849784199362</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07362563643676479</v>
+        <v>0.07356795126151747</v>
       </c>
       <c r="C19">
-        <v>446.2546275649252</v>
+        <v>442.0360199381382</v>
       </c>
       <c r="D19">
-        <v>502.4141241889239</v>
+        <v>503.4578398929604</v>
       </c>
       <c r="E19">
-        <v>48.82716354165301</v>
+        <v>54.08948687247647</v>
       </c>
       <c r="F19">
-        <v>89.45949662399879</v>
+        <v>94.72181995482225</v>
       </c>
       <c r="G19">
         <v>33.3</v>
@@ -2845,28 +2845,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M19">
-        <v>4.634001925123137</v>
+        <v>4.906590273659792</v>
       </c>
       <c r="N19">
-        <v>45.91599807487687</v>
+        <v>45.64340972634022</v>
       </c>
       <c r="O19">
-        <v>6.703735718932023</v>
+        <v>6.663937820045671</v>
       </c>
       <c r="P19">
-        <v>39.21226235594485</v>
+        <v>38.97947190629455</v>
       </c>
       <c r="Q19">
-        <v>62.01226235594486</v>
+        <v>61.77947190629455</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07964495474309011</v>
+        <v>0.08000640885550911</v>
       </c>
       <c r="T19">
-        <v>0.7816386776695173</v>
+        <v>0.7899863477022889</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.90849784199362</v>
+        <v>10.30247018410508</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07356795126151748</v>
+        <v>0.07378610808627016</v>
       </c>
       <c r="C20">
-        <v>442.0360199381378</v>
+        <v>432.849150778744</v>
       </c>
       <c r="D20">
-        <v>503.4578398929601</v>
+        <v>499.5332940643898</v>
       </c>
       <c r="E20">
-        <v>54.08948687247646</v>
+        <v>59.35181020329992</v>
       </c>
       <c r="F20">
-        <v>94.72181995482224</v>
+        <v>99.9841432856457</v>
       </c>
       <c r="G20">
         <v>33.3</v>
@@ -2927,45 +2927,45 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M20">
-        <v>4.906590273659792</v>
+        <v>5.349151665782045</v>
       </c>
       <c r="N20">
-        <v>45.64340972634022</v>
+        <v>45.20084833421797</v>
       </c>
       <c r="O20">
-        <v>6.663937820045671</v>
+        <v>6.599323856795823</v>
       </c>
       <c r="P20">
-        <v>38.97947190629455</v>
+        <v>38.60152447742215</v>
       </c>
       <c r="Q20">
-        <v>61.77947190629455</v>
+        <v>61.40152447742214</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08000640885550911</v>
+        <v>0.08037678776082735</v>
       </c>
       <c r="T20">
-        <v>0.7899863477022889</v>
+        <v>0.7985401330445117</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.146</v>
       </c>
       <c r="W20">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.30247018410508</v>
+        <v>9.45009660566609</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07378610808627016</v>
+        <v>0.07374294091102285</v>
       </c>
       <c r="C21">
-        <v>432.849150778744</v>
+        <v>428.3585229296313</v>
       </c>
       <c r="D21">
-        <v>499.5332940643898</v>
+        <v>500.3049895461004</v>
       </c>
       <c r="E21">
-        <v>59.35181020329992</v>
+        <v>64.61413353412338</v>
       </c>
       <c r="F21">
-        <v>99.9841432856457</v>
+        <v>105.2464666164692</v>
       </c>
       <c r="G21">
         <v>33.3</v>
@@ -3009,28 +3009,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M21">
-        <v>5.349151665782045</v>
+        <v>5.6306859639811</v>
       </c>
       <c r="N21">
-        <v>45.20084833421797</v>
+        <v>44.91931403601891</v>
       </c>
       <c r="O21">
-        <v>6.599323856795823</v>
+        <v>6.55821984925876</v>
       </c>
       <c r="P21">
-        <v>38.60152447742215</v>
+        <v>38.36109418676015</v>
       </c>
       <c r="Q21">
-        <v>61.40152447742214</v>
+        <v>61.16109418676015</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08037678776082735</v>
+        <v>0.08075642613877855</v>
       </c>
       <c r="T21">
-        <v>0.7985401330445117</v>
+        <v>0.8073077630202898</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.45009660566609</v>
+        <v>8.977591775382784</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07374294091102285</v>
+        <v>0.07369977373577553</v>
       </c>
       <c r="C22">
-        <v>428.3585229296313</v>
+        <v>423.8702830507158</v>
       </c>
       <c r="D22">
-        <v>500.3049895461004</v>
+        <v>501.0790729980084</v>
       </c>
       <c r="E22">
-        <v>64.61413353412338</v>
+        <v>69.87645686494685</v>
       </c>
       <c r="F22">
-        <v>105.2464666164692</v>
+        <v>110.5087899472926</v>
       </c>
       <c r="G22">
         <v>33.3</v>
@@ -3091,28 +3091,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M22">
-        <v>5.6306859639811</v>
+        <v>5.912220262180155</v>
       </c>
       <c r="N22">
-        <v>44.91931403601891</v>
+        <v>44.63777973781986</v>
       </c>
       <c r="O22">
-        <v>6.55821984925876</v>
+        <v>6.517115841721698</v>
       </c>
       <c r="P22">
-        <v>38.36109418676015</v>
+        <v>38.12066389609816</v>
       </c>
       <c r="Q22">
-        <v>61.16109418676015</v>
+        <v>60.92066389609816</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08075642613877855</v>
+        <v>0.08114567561490572</v>
       </c>
       <c r="T22">
-        <v>0.8073077630202898</v>
+        <v>0.8162973583119105</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.977591775382784</v>
+        <v>8.550087405126462</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07369977373577553</v>
+        <v>0.07365660656052822</v>
       </c>
       <c r="C23">
-        <v>423.8702830507158</v>
+        <v>419.3844422433422</v>
       </c>
       <c r="D23">
-        <v>501.0790729980084</v>
+        <v>501.8555555214583</v>
       </c>
       <c r="E23">
-        <v>69.87645686494683</v>
+        <v>75.13878019577029</v>
       </c>
       <c r="F23">
-        <v>110.5087899472926</v>
+        <v>115.7711132781161</v>
       </c>
       <c r="G23">
         <v>33.3</v>
@@ -3173,28 +3173,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M23">
-        <v>5.912220262180155</v>
+        <v>6.19375456037921</v>
       </c>
       <c r="N23">
-        <v>44.63777973781986</v>
+        <v>44.3562454396208</v>
       </c>
       <c r="O23">
-        <v>6.517115841721698</v>
+        <v>6.476011834184637</v>
       </c>
       <c r="P23">
-        <v>38.12066389609816</v>
+        <v>37.88023360543616</v>
       </c>
       <c r="Q23">
-        <v>60.92066389609816</v>
+        <v>60.68023360543616</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08114567561490572</v>
+        <v>0.08154490584683104</v>
       </c>
       <c r="T23">
-        <v>0.8162973583119105</v>
+        <v>0.8255174560469062</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.550087405126462</v>
+        <v>8.161447068529803</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07365660656052822</v>
+        <v>0.07361343938528089</v>
       </c>
       <c r="C24">
-        <v>419.3844422433422</v>
+        <v>414.9010116777732</v>
       </c>
       <c r="D24">
-        <v>501.8555555214583</v>
+        <v>502.6344482867128</v>
       </c>
       <c r="E24">
-        <v>75.13878019577029</v>
+        <v>80.40110352659376</v>
       </c>
       <c r="F24">
-        <v>115.7711132781161</v>
+        <v>121.0334366089395</v>
       </c>
       <c r="G24">
         <v>33.3</v>
@@ -3255,28 +3255,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M24">
-        <v>6.19375456037921</v>
+        <v>6.475288858578265</v>
       </c>
       <c r="N24">
-        <v>44.3562454396208</v>
+        <v>44.07471114142174</v>
       </c>
       <c r="O24">
-        <v>6.476011834184637</v>
+        <v>6.434907826647574</v>
       </c>
       <c r="P24">
-        <v>37.88023360543616</v>
+        <v>37.63980331477417</v>
       </c>
       <c r="Q24">
-        <v>60.68023360543616</v>
+        <v>60.43980331477417</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08154490584683104</v>
+        <v>0.08195450569516999</v>
       </c>
       <c r="T24">
-        <v>0.8255174560469062</v>
+        <v>0.8349770368399536</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.161447068529803</v>
+        <v>7.806601543811117</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07361343938528089</v>
+        <v>0.07373424021003358</v>
       </c>
       <c r="C25">
-        <v>414.9010116777732</v>
+        <v>407.4650600167853</v>
       </c>
       <c r="D25">
-        <v>502.6344482867128</v>
+        <v>500.4608199565483</v>
       </c>
       <c r="E25">
-        <v>80.40110352659376</v>
+        <v>85.66342685741722</v>
       </c>
       <c r="F25">
-        <v>121.0334366089395</v>
+        <v>126.295759939763</v>
       </c>
       <c r="G25">
         <v>33.3</v>
@@ -3337,45 +3337,45 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M25">
-        <v>6.475288858578265</v>
+        <v>6.857859764729131</v>
       </c>
       <c r="N25">
-        <v>44.07471114142174</v>
+        <v>43.69214023527088</v>
       </c>
       <c r="O25">
-        <v>6.434907826647574</v>
+        <v>6.379052474349549</v>
       </c>
       <c r="P25">
-        <v>37.63980331477417</v>
+        <v>37.31308776092133</v>
       </c>
       <c r="Q25">
-        <v>60.43980331477417</v>
+        <v>60.11308776092133</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08195450569516999</v>
+        <v>0.08237488448688629</v>
       </c>
       <c r="T25">
-        <v>0.8349770368399536</v>
+        <v>0.8446855539696603</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.146</v>
       </c>
       <c r="W25">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.806601543811117</v>
+        <v>7.37110435824093</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07373424021003358</v>
+        <v>0.07369790503478627</v>
       </c>
       <c r="C26">
-        <v>407.4650600167853</v>
+        <v>402.8545537874562</v>
       </c>
       <c r="D26">
-        <v>500.4608199565483</v>
+        <v>501.1126370580426</v>
       </c>
       <c r="E26">
-        <v>85.66342685741721</v>
+        <v>90.92575018824067</v>
       </c>
       <c r="F26">
-        <v>126.295759939763</v>
+        <v>131.5580832705865</v>
       </c>
       <c r="G26">
         <v>33.3</v>
@@ -3419,28 +3419,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M26">
-        <v>6.85785976472913</v>
+        <v>7.143603921592844</v>
       </c>
       <c r="N26">
-        <v>43.69214023527088</v>
+        <v>43.40639607840717</v>
       </c>
       <c r="O26">
-        <v>6.379052474349549</v>
+        <v>6.337333827447447</v>
       </c>
       <c r="P26">
-        <v>37.31308776092133</v>
+        <v>37.06906225095972</v>
       </c>
       <c r="Q26">
-        <v>60.11308776092133</v>
+        <v>59.86906225095973</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08237488448688629</v>
+        <v>0.08280647337971503</v>
       </c>
       <c r="T26">
-        <v>0.8446855539696603</v>
+        <v>0.8546529648894924</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.37110435824093</v>
+        <v>7.076260183911293</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07369790503478627</v>
+        <v>0.07366156985953895</v>
       </c>
       <c r="C27">
-        <v>402.8545537874562</v>
+        <v>398.245747669695</v>
       </c>
       <c r="D27">
-        <v>501.1126370580426</v>
+        <v>501.7661542711049</v>
       </c>
       <c r="E27">
-        <v>90.92575018824067</v>
+        <v>96.18807351906412</v>
       </c>
       <c r="F27">
-        <v>131.5580832705865</v>
+        <v>136.8204066014099</v>
       </c>
       <c r="G27">
         <v>33.3</v>
@@ -3501,28 +3501,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M27">
-        <v>7.143603921592844</v>
+        <v>7.429348078456558</v>
       </c>
       <c r="N27">
-        <v>43.40639607840717</v>
+        <v>43.12065192154346</v>
       </c>
       <c r="O27">
-        <v>6.337333827447447</v>
+        <v>6.295615180545344</v>
       </c>
       <c r="P27">
-        <v>37.06906225095972</v>
+        <v>36.82503674099812</v>
       </c>
       <c r="Q27">
-        <v>59.86906225095973</v>
+        <v>59.62503674099811</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08280647337971503</v>
+        <v>0.08324972683721479</v>
       </c>
       <c r="T27">
-        <v>0.8546529648894924</v>
+        <v>0.8648897652936443</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.076260183911293</v>
+        <v>6.804096330683936</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07366156985953895</v>
+        <v>0.07362523468429163</v>
       </c>
       <c r="C28">
-        <v>398.245747669695</v>
+        <v>393.6386483236994</v>
       </c>
       <c r="D28">
-        <v>501.7661542711049</v>
+        <v>502.4213782559328</v>
       </c>
       <c r="E28">
-        <v>96.18807351906412</v>
+        <v>101.4503968498876</v>
       </c>
       <c r="F28">
-        <v>136.8204066014099</v>
+        <v>142.0827299322334</v>
       </c>
       <c r="G28">
         <v>33.3</v>
@@ -3583,28 +3583,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M28">
-        <v>7.429348078456558</v>
+        <v>7.715092235320273</v>
       </c>
       <c r="N28">
-        <v>43.12065192154346</v>
+        <v>42.83490776467974</v>
       </c>
       <c r="O28">
-        <v>6.295615180545344</v>
+        <v>6.253896533643242</v>
       </c>
       <c r="P28">
-        <v>36.82503674099812</v>
+        <v>36.5810112310365</v>
       </c>
       <c r="Q28">
-        <v>59.62503674099811</v>
+        <v>59.3810112310365</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08324972683721479</v>
+        <v>0.08370512422505703</v>
       </c>
       <c r="T28">
-        <v>0.8648897652936443</v>
+        <v>0.8754070259828415</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.804096330683936</v>
+        <v>6.552092762880826</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07362523468429163</v>
+        <v>0.07358889950904433</v>
       </c>
       <c r="C29">
-        <v>393.6386483236994</v>
+        <v>389.0332624445005</v>
       </c>
       <c r="D29">
-        <v>502.4213782559328</v>
+        <v>503.0783157075572</v>
       </c>
       <c r="E29">
-        <v>101.4503968498876</v>
+        <v>106.712720180711</v>
       </c>
       <c r="F29">
-        <v>142.0827299322334</v>
+        <v>147.3450532630568</v>
       </c>
       <c r="G29">
         <v>33.3</v>
@@ -3665,28 +3665,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M29">
-        <v>7.715092235320273</v>
+        <v>8.000836392183986</v>
       </c>
       <c r="N29">
-        <v>42.83490776467974</v>
+        <v>42.54916360781603</v>
       </c>
       <c r="O29">
-        <v>6.253896533643242</v>
+        <v>6.21217788674114</v>
       </c>
       <c r="P29">
-        <v>36.5810112310365</v>
+        <v>36.33698572107489</v>
       </c>
       <c r="Q29">
-        <v>59.3810112310365</v>
+        <v>59.13698572107489</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08370512422505703</v>
+        <v>0.08417317154033935</v>
       </c>
       <c r="T29">
-        <v>0.8754070259828415</v>
+        <v>0.8862164328022942</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.552092762880826</v>
+        <v>6.318089449920797</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07358889950904433</v>
+        <v>0.07380022433379702</v>
       </c>
       <c r="C30">
-        <v>389.0332624445005</v>
+        <v>379.9740789301159</v>
       </c>
       <c r="D30">
-        <v>503.0783157075572</v>
+        <v>499.2814555239962</v>
       </c>
       <c r="E30">
-        <v>106.712720180711</v>
+        <v>111.9750435115345</v>
       </c>
       <c r="F30">
-        <v>147.3450532630568</v>
+        <v>152.6073765938803</v>
       </c>
       <c r="G30">
         <v>33.3</v>
@@ -3747,45 +3747,45 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M30">
-        <v>8.000836392183986</v>
+        <v>8.439187925641582</v>
       </c>
       <c r="N30">
-        <v>42.54916360781603</v>
+        <v>42.11081207435843</v>
       </c>
       <c r="O30">
-        <v>6.21217788674114</v>
+        <v>6.14817856285633</v>
       </c>
       <c r="P30">
-        <v>36.33698572107489</v>
+        <v>35.9626335115021</v>
       </c>
       <c r="Q30">
-        <v>59.13698572107489</v>
+        <v>58.7626335115021</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08417317154033935</v>
+        <v>0.08465440328703804</v>
       </c>
       <c r="T30">
-        <v>0.8862164328022942</v>
+        <v>0.8973303299546891</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.146</v>
       </c>
       <c r="W30">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.318089449920797</v>
+        <v>5.989912826376241</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.073800224333797</v>
+        <v>0.07377242915854969</v>
       </c>
       <c r="C31">
-        <v>379.9740789301161</v>
+        <v>375.2078732398223</v>
       </c>
       <c r="D31">
-        <v>499.2814555239964</v>
+        <v>499.777573164526</v>
       </c>
       <c r="E31">
-        <v>111.9750435115345</v>
+        <v>117.2373668423579</v>
       </c>
       <c r="F31">
-        <v>152.6073765938803</v>
+        <v>157.8696999247037</v>
       </c>
       <c r="G31">
         <v>33.3</v>
@@ -3829,28 +3829,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M31">
-        <v>8.43918792564158</v>
+        <v>8.730194405836116</v>
       </c>
       <c r="N31">
-        <v>42.11081207435844</v>
+        <v>41.8198055941639</v>
       </c>
       <c r="O31">
-        <v>6.148178562856331</v>
+        <v>6.105691616747928</v>
       </c>
       <c r="P31">
-        <v>35.9626335115021</v>
+        <v>35.71411397741597</v>
       </c>
       <c r="Q31">
-        <v>58.7626335115021</v>
+        <v>58.51411397741597</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08465440328703804</v>
+        <v>0.08514938451221385</v>
       </c>
       <c r="T31">
-        <v>0.8973303299546891</v>
+        <v>0.908761767025724</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.989912826376242</v>
+        <v>5.790249065497035</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07377242915854969</v>
+        <v>0.07374463398330237</v>
       </c>
       <c r="C32">
-        <v>375.2078732398223</v>
+        <v>370.4426544779507</v>
       </c>
       <c r="D32">
-        <v>499.777573164526</v>
+        <v>500.2746777334779</v>
       </c>
       <c r="E32">
-        <v>117.2373668423579</v>
+        <v>122.4996901731814</v>
       </c>
       <c r="F32">
-        <v>157.8696999247037</v>
+        <v>163.1320232555272</v>
       </c>
       <c r="G32">
         <v>33.3</v>
@@ -3911,28 +3911,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M32">
-        <v>8.730194405836116</v>
+        <v>9.021200886030655</v>
       </c>
       <c r="N32">
-        <v>41.8198055941639</v>
+        <v>41.52879911396936</v>
       </c>
       <c r="O32">
-        <v>6.105691616747928</v>
+        <v>6.063204670639526</v>
       </c>
       <c r="P32">
-        <v>35.71411397741597</v>
+        <v>35.46559444332983</v>
       </c>
       <c r="Q32">
-        <v>58.51411397741597</v>
+        <v>58.26559444332983</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08514938451221385</v>
+        <v>0.08565871301927881</v>
       </c>
       <c r="T32">
-        <v>0.908761767025724</v>
+        <v>0.9205245500988178</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.790249065497035</v>
+        <v>5.603466837577774</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07374463398330237</v>
+        <v>0.07371683880805506</v>
       </c>
       <c r="C33">
-        <v>370.4426544779507</v>
+        <v>365.678425592383</v>
       </c>
       <c r="D33">
-        <v>500.2746777334779</v>
+        <v>500.7727721787336</v>
       </c>
       <c r="E33">
-        <v>122.4996901731814</v>
+        <v>127.7620135040049</v>
       </c>
       <c r="F33">
-        <v>163.1320232555272</v>
+        <v>168.3943465863507</v>
       </c>
       <c r="G33">
         <v>33.3</v>
@@ -3993,28 +3993,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M33">
-        <v>9.021200886030655</v>
+        <v>9.312207366225191</v>
       </c>
       <c r="N33">
-        <v>41.52879911396936</v>
+        <v>41.23779263377482</v>
       </c>
       <c r="O33">
-        <v>6.063204670639526</v>
+        <v>6.020717724531123</v>
       </c>
       <c r="P33">
-        <v>35.46559444332983</v>
+        <v>35.21707490924369</v>
       </c>
       <c r="Q33">
-        <v>58.26559444332983</v>
+        <v>58.01707490924369</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08565871301927881</v>
+        <v>0.08618302177655157</v>
       </c>
       <c r="T33">
-        <v>0.9205245500988178</v>
+        <v>0.9326332973799437</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.603466837577774</v>
+        <v>5.428358498903469</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07371683880805506</v>
+        <v>0.07368904363280775</v>
       </c>
       <c r="C34">
-        <v>365.678425592383</v>
+        <v>360.9151895427533</v>
       </c>
       <c r="D34">
-        <v>500.7727721787336</v>
+        <v>501.2718594599274</v>
       </c>
       <c r="E34">
-        <v>127.7620135040049</v>
+        <v>133.0243368348283</v>
       </c>
       <c r="F34">
-        <v>168.3943465863507</v>
+        <v>173.6566699171741</v>
       </c>
       <c r="G34">
         <v>33.3</v>
@@ -4075,28 +4075,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M34">
-        <v>9.312207366225191</v>
+        <v>9.603213846419729</v>
       </c>
       <c r="N34">
-        <v>41.23779263377482</v>
+        <v>40.94678615358028</v>
       </c>
       <c r="O34">
-        <v>6.020717724531123</v>
+        <v>5.978230778422721</v>
       </c>
       <c r="P34">
-        <v>35.21707490924369</v>
+        <v>34.96855537515756</v>
       </c>
       <c r="Q34">
-        <v>58.01707490924369</v>
+        <v>57.76855537515756</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08618302177655157</v>
+        <v>0.0867229815415041</v>
       </c>
       <c r="T34">
-        <v>0.9326332973799437</v>
+        <v>0.9451034998037898</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.428358498903469</v>
+        <v>5.263862786815485</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07368904363280775</v>
+        <v>0.07366124845756042</v>
       </c>
       <c r="C35">
-        <v>360.9151895427533</v>
+        <v>356.1529493005058</v>
       </c>
       <c r="D35">
-        <v>501.2718594599274</v>
+        <v>501.7719425485035</v>
       </c>
       <c r="E35">
-        <v>133.0243368348283</v>
+        <v>138.2866601656518</v>
       </c>
       <c r="F35">
-        <v>173.6566699171741</v>
+        <v>178.9189932479976</v>
       </c>
       <c r="G35">
         <v>33.3</v>
@@ -4157,28 +4157,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M35">
-        <v>9.603213846419729</v>
+        <v>9.894220326614267</v>
       </c>
       <c r="N35">
-        <v>40.94678615358028</v>
+        <v>40.65577967338574</v>
       </c>
       <c r="O35">
-        <v>5.978230778422721</v>
+        <v>5.935743832314318</v>
       </c>
       <c r="P35">
-        <v>34.96855537515756</v>
+        <v>34.72003584107143</v>
       </c>
       <c r="Q35">
-        <v>57.76855537515756</v>
+        <v>57.52003584107143</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0867229815415041</v>
+        <v>0.08727930372357641</v>
       </c>
       <c r="T35">
-        <v>0.9451034998037898</v>
+        <v>0.9579515871495707</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.263862786815485</v>
+        <v>5.109043293085618</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07366124845756042</v>
+        <v>0.0736334532823131</v>
       </c>
       <c r="C36">
-        <v>356.1529493005058</v>
+        <v>351.391707848954</v>
       </c>
       <c r="D36">
-        <v>501.7719425485035</v>
+        <v>502.2730244277751</v>
       </c>
       <c r="E36">
-        <v>138.2866601656518</v>
+        <v>143.5489834964753</v>
       </c>
       <c r="F36">
-        <v>178.9189932479976</v>
+        <v>184.1813165788211</v>
       </c>
       <c r="G36">
         <v>33.3</v>
@@ -4239,28 +4239,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M36">
-        <v>9.894220326614267</v>
+        <v>10.1852268068088</v>
       </c>
       <c r="N36">
-        <v>40.65577967338574</v>
+        <v>40.3647731931912</v>
       </c>
       <c r="O36">
-        <v>5.935743832314318</v>
+        <v>5.893256886205916</v>
       </c>
       <c r="P36">
-        <v>34.72003584107143</v>
+        <v>34.47151630698529</v>
       </c>
       <c r="Q36">
-        <v>57.52003584107143</v>
+        <v>57.27151630698529</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08727930372357641</v>
+        <v>0.08785274351125094</v>
       </c>
       <c r="T36">
-        <v>0.9579515871495707</v>
+        <v>0.9711950002598371</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.109043293085618</v>
+        <v>4.963070627568886</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0736334532823131</v>
+        <v>0.07360565810706579</v>
       </c>
       <c r="C37">
-        <v>351.391707848954</v>
+        <v>346.6314681833405</v>
       </c>
       <c r="D37">
-        <v>502.2730244277751</v>
+        <v>502.775108092985</v>
       </c>
       <c r="E37">
-        <v>143.5489834964753</v>
+        <v>148.8113068272987</v>
       </c>
       <c r="F37">
-        <v>184.1813165788211</v>
+        <v>189.4436399096445</v>
       </c>
       <c r="G37">
         <v>33.3</v>
@@ -4321,28 +4321,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M37">
-        <v>10.1852268068088</v>
+        <v>10.47623328700334</v>
       </c>
       <c r="N37">
-        <v>40.3647731931912</v>
+        <v>40.07376671299667</v>
       </c>
       <c r="O37">
-        <v>5.893256886205916</v>
+        <v>5.850769940097514</v>
       </c>
       <c r="P37">
-        <v>34.47151630698529</v>
+        <v>34.22299677289916</v>
       </c>
       <c r="Q37">
-        <v>57.27151630698529</v>
+        <v>57.02299677289916</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08785274351125094</v>
+        <v>0.08844410329229031</v>
       </c>
       <c r="T37">
-        <v>0.9711950002598371</v>
+        <v>0.9848522700297994</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.963070627568886</v>
+        <v>4.825207554580862</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07360565810706581</v>
+        <v>0.07357786293181849</v>
       </c>
       <c r="C38">
-        <v>346.6314681833403</v>
+        <v>341.8722333108959</v>
       </c>
       <c r="D38">
-        <v>502.7751080929848</v>
+        <v>503.2781965513638</v>
       </c>
       <c r="E38">
-        <v>148.8113068272987</v>
+        <v>154.0736301581222</v>
       </c>
       <c r="F38">
-        <v>189.4436399096445</v>
+        <v>194.705963240468</v>
       </c>
       <c r="G38">
         <v>33.3</v>
@@ -4403,28 +4403,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M38">
-        <v>10.47623328700334</v>
+        <v>10.76723976719788</v>
       </c>
       <c r="N38">
-        <v>40.07376671299667</v>
+        <v>39.78276023280213</v>
       </c>
       <c r="O38">
-        <v>5.850769940097514</v>
+        <v>5.808282993989111</v>
       </c>
       <c r="P38">
-        <v>34.22299677289916</v>
+        <v>33.97447723881302</v>
       </c>
       <c r="Q38">
-        <v>57.02299677289916</v>
+        <v>56.77447723881302</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08844410329229031</v>
+        <v>0.08905423639971188</v>
       </c>
       <c r="T38">
-        <v>0.9848522700297994</v>
+        <v>0.998943103919443</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.825207554580862</v>
+        <v>4.69479653959219</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07357786293181849</v>
+        <v>0.07355006775657118</v>
       </c>
       <c r="C39">
-        <v>341.8722333108959</v>
+        <v>337.1140062508998</v>
       </c>
       <c r="D39">
-        <v>503.2781965513638</v>
+        <v>503.7822928221912</v>
       </c>
       <c r="E39">
-        <v>154.0736301581222</v>
+        <v>159.3359534889456</v>
       </c>
       <c r="F39">
-        <v>194.705963240468</v>
+        <v>199.9682865712914</v>
       </c>
       <c r="G39">
         <v>33.3</v>
@@ -4485,28 +4485,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M39">
-        <v>10.76723976719788</v>
+        <v>11.05824624739241</v>
       </c>
       <c r="N39">
-        <v>39.78276023280213</v>
+        <v>39.49175375260759</v>
       </c>
       <c r="O39">
-        <v>5.808282993989111</v>
+        <v>5.765796047880708</v>
       </c>
       <c r="P39">
-        <v>33.97447723881302</v>
+        <v>33.72595770472689</v>
       </c>
       <c r="Q39">
-        <v>56.77447723881302</v>
+        <v>56.52595770472689</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08905423639971188</v>
+        <v>0.08968405122027609</v>
       </c>
       <c r="T39">
-        <v>0.998943103919443</v>
+        <v>1.013488480837785</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.69479653959219</v>
+        <v>4.571249262234501</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07355006775657118</v>
+        <v>0.07435492258132385</v>
       </c>
       <c r="C40">
-        <v>337.1140062508998</v>
+        <v>317.6519732956453</v>
       </c>
       <c r="D40">
-        <v>503.7822928221912</v>
+        <v>489.5825831977602</v>
       </c>
       <c r="E40">
-        <v>159.3359534889456</v>
+        <v>164.5982768197691</v>
       </c>
       <c r="F40">
-        <v>199.9682865712914</v>
+        <v>205.2306099021149</v>
       </c>
       <c r="G40">
         <v>33.3</v>
@@ -4567,45 +4567,45 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M40">
-        <v>11.05824624739241</v>
+        <v>11.86232925234224</v>
       </c>
       <c r="N40">
-        <v>39.49175375260759</v>
+        <v>38.68767074765777</v>
       </c>
       <c r="O40">
-        <v>5.765796047880708</v>
+        <v>5.648399929158034</v>
       </c>
       <c r="P40">
-        <v>33.72595770472689</v>
+        <v>33.03927081849974</v>
       </c>
       <c r="Q40">
-        <v>56.52595770472689</v>
+        <v>55.83927081849974</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08968405122027609</v>
+        <v>0.09033451570708829</v>
       </c>
       <c r="T40">
-        <v>1.013488480837785</v>
+        <v>1.028510755360007</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.146</v>
       </c>
       <c r="W40">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.571249262234501</v>
+        <v>4.261389051397204</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07435492258132385</v>
+        <v>0.07434847740607653</v>
       </c>
       <c r="C41">
-        <v>317.6519732956453</v>
+        <v>312.5001793461919</v>
       </c>
       <c r="D41">
-        <v>489.5825831977602</v>
+        <v>489.6931125791302</v>
       </c>
       <c r="E41">
-        <v>164.5982768197691</v>
+        <v>169.8606001505925</v>
       </c>
       <c r="F41">
-        <v>205.2306099021149</v>
+        <v>210.4929332329383</v>
       </c>
       <c r="G41">
         <v>33.3</v>
@@ -4649,28 +4649,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M41">
-        <v>11.86232925234224</v>
+        <v>12.16649154086384</v>
       </c>
       <c r="N41">
-        <v>38.68767074765777</v>
+        <v>38.38350845913617</v>
       </c>
       <c r="O41">
-        <v>5.648399929158034</v>
+        <v>5.603992235033881</v>
       </c>
       <c r="P41">
-        <v>33.03927081849974</v>
+        <v>32.7795162241023</v>
       </c>
       <c r="Q41">
-        <v>55.83927081849974</v>
+        <v>55.57951622410229</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09033451570708829</v>
+        <v>0.09100666234346089</v>
       </c>
       <c r="T41">
-        <v>1.028510755360007</v>
+        <v>1.044033772366302</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.261389051397204</v>
+        <v>4.154854325112274</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07434847740607653</v>
+        <v>0.07434203223082922</v>
       </c>
       <c r="C42">
-        <v>312.5001793461919</v>
+        <v>307.3484353147836</v>
       </c>
       <c r="D42">
-        <v>489.6931125791302</v>
+        <v>489.8036918785455</v>
       </c>
       <c r="E42">
-        <v>169.8606001505925</v>
+        <v>175.122923481416</v>
       </c>
       <c r="F42">
-        <v>210.4929332329383</v>
+        <v>215.7552565637618</v>
       </c>
       <c r="G42">
         <v>33.3</v>
@@ -4731,28 +4731,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M42">
-        <v>12.16649154086384</v>
+        <v>12.47065382938543</v>
       </c>
       <c r="N42">
-        <v>38.38350845913617</v>
+        <v>38.07934617061458</v>
       </c>
       <c r="O42">
-        <v>5.603992235033881</v>
+        <v>5.559584540909728</v>
       </c>
       <c r="P42">
-        <v>32.7795162241023</v>
+        <v>32.51976162970485</v>
       </c>
       <c r="Q42">
-        <v>55.57951622410229</v>
+        <v>55.31976162970486</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09100666234346089</v>
+        <v>0.09170159361157496</v>
       </c>
       <c r="T42">
-        <v>1.044033772366302</v>
+        <v>1.060082993338914</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.154854325112274</v>
+        <v>4.053516414743682</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07434203223082922</v>
+        <v>0.07559096705558191</v>
       </c>
       <c r="C43">
-        <v>307.3484353147836</v>
+        <v>281.5519384226179</v>
       </c>
       <c r="D43">
-        <v>489.8036918785455</v>
+        <v>469.2695183172031</v>
       </c>
       <c r="E43">
-        <v>175.122923481416</v>
+        <v>180.3852468122395</v>
       </c>
       <c r="F43">
-        <v>215.7552565637618</v>
+        <v>221.0175798945853</v>
       </c>
       <c r="G43">
         <v>33.3</v>
@@ -4813,45 +4813,45 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M43">
-        <v>12.47065382938543</v>
+        <v>13.54837764753808</v>
       </c>
       <c r="N43">
-        <v>38.07934617061458</v>
+        <v>37.00162235246194</v>
       </c>
       <c r="O43">
-        <v>5.559584540909728</v>
+        <v>5.402236863459442</v>
       </c>
       <c r="P43">
-        <v>32.51976162970485</v>
+        <v>31.59938548900249</v>
       </c>
       <c r="Q43">
-        <v>55.31976162970486</v>
+        <v>54.3993854890025</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09170159361157496</v>
+        <v>0.09242048802686537</v>
       </c>
       <c r="T43">
-        <v>1.060082993338914</v>
+        <v>1.076685635724373</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.146</v>
       </c>
       <c r="W43">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.053516414743682</v>
+        <v>3.731074030785201</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07559096705558192</v>
+        <v>0.0756144118803346</v>
       </c>
       <c r="C44">
-        <v>281.5519384226177</v>
+        <v>275.9206008827305</v>
       </c>
       <c r="D44">
-        <v>469.2695183172029</v>
+        <v>468.9005041081392</v>
       </c>
       <c r="E44">
-        <v>180.3852468122394</v>
+        <v>185.6475701430629</v>
       </c>
       <c r="F44">
-        <v>221.0175798945852</v>
+        <v>226.2799032254087</v>
       </c>
       <c r="G44">
         <v>33.3</v>
@@ -4895,28 +4895,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M44">
-        <v>13.54837764753808</v>
+        <v>13.87095806771755</v>
       </c>
       <c r="N44">
-        <v>37.00162235246194</v>
+        <v>36.67904193228246</v>
       </c>
       <c r="O44">
-        <v>5.402236863459442</v>
+        <v>5.355140122113239</v>
       </c>
       <c r="P44">
-        <v>31.59938548900249</v>
+        <v>31.32390181016922</v>
       </c>
       <c r="Q44">
-        <v>54.3993854890025</v>
+        <v>54.12390181016922</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09242048802686537</v>
+        <v>0.09316460680760455</v>
       </c>
       <c r="T44">
-        <v>1.076685635724373</v>
+        <v>1.093870826965463</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.731074030785202</v>
+        <v>3.644304867278569</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0756144118803346</v>
+        <v>0.07563785670508728</v>
       </c>
       <c r="C45">
-        <v>275.9206008827305</v>
+        <v>270.2898432419659</v>
       </c>
       <c r="D45">
-        <v>468.9005041081392</v>
+        <v>468.5320697981981</v>
       </c>
       <c r="E45">
-        <v>185.6475701430629</v>
+        <v>190.9098934738864</v>
       </c>
       <c r="F45">
-        <v>226.2799032254087</v>
+        <v>231.5422265562322</v>
       </c>
       <c r="G45">
         <v>33.3</v>
@@ -4977,28 +4977,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M45">
-        <v>13.87095806771755</v>
+        <v>14.19353848789703</v>
       </c>
       <c r="N45">
-        <v>36.67904193228246</v>
+        <v>36.35646151210298</v>
       </c>
       <c r="O45">
-        <v>5.355140122113239</v>
+        <v>5.308043380767035</v>
       </c>
       <c r="P45">
-        <v>31.32390181016922</v>
+        <v>31.04841813133595</v>
       </c>
       <c r="Q45">
-        <v>54.12390181016922</v>
+        <v>53.84841813133595</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09316460680760455</v>
+        <v>0.09393530125908442</v>
       </c>
       <c r="T45">
-        <v>1.093870826965463</v>
+        <v>1.111669775036592</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.644304867278569</v>
+        <v>3.561479756658601</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07563785670508728</v>
+        <v>0.07673734152983996</v>
       </c>
       <c r="C46">
-        <v>270.2898432419659</v>
+        <v>248.3763186385247</v>
       </c>
       <c r="D46">
-        <v>468.5320697981981</v>
+        <v>451.8808685255803</v>
       </c>
       <c r="E46">
-        <v>190.9098934738864</v>
+        <v>196.1722168047098</v>
       </c>
       <c r="F46">
-        <v>231.5422265562322</v>
+        <v>236.8045498870556</v>
       </c>
       <c r="G46">
         <v>33.3</v>
@@ -5059,45 +5059,45 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M46">
-        <v>14.19353848789703</v>
+        <v>15.17917164776027</v>
       </c>
       <c r="N46">
-        <v>36.35646151210298</v>
+        <v>35.37082835223974</v>
       </c>
       <c r="O46">
-        <v>5.308043380767035</v>
+        <v>5.164140939427002</v>
       </c>
       <c r="P46">
-        <v>31.04841813133595</v>
+        <v>30.20668741281274</v>
       </c>
       <c r="Q46">
-        <v>53.84841813133595</v>
+        <v>53.00668741281274</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09393530125908442</v>
+        <v>0.09473402096334538</v>
       </c>
       <c r="T46">
-        <v>1.111669775036592</v>
+        <v>1.130115957583034</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.146</v>
       </c>
       <c r="W46">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.561479756658601</v>
+        <v>3.33022125139871</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07673734152983996</v>
+        <v>0.07678469835459266</v>
       </c>
       <c r="C47">
-        <v>248.3763186385247</v>
+        <v>242.4233433331375</v>
       </c>
       <c r="D47">
-        <v>451.8808685255803</v>
+        <v>451.1902165510165</v>
       </c>
       <c r="E47">
-        <v>196.1722168047098</v>
+        <v>201.4345401355333</v>
       </c>
       <c r="F47">
-        <v>236.8045498870556</v>
+        <v>242.0668732178791</v>
       </c>
       <c r="G47">
         <v>33.3</v>
@@ -5141,28 +5141,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M47">
-        <v>15.17917164776027</v>
+        <v>15.51648657326605</v>
       </c>
       <c r="N47">
-        <v>35.37082835223974</v>
+        <v>35.03351342673396</v>
       </c>
       <c r="O47">
-        <v>5.164140939427002</v>
+        <v>5.114892960303158</v>
       </c>
       <c r="P47">
-        <v>30.20668741281274</v>
+        <v>29.9186204664308</v>
       </c>
       <c r="Q47">
-        <v>53.00668741281274</v>
+        <v>52.71862046643081</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09473402096334538</v>
+        <v>0.09556232287887528</v>
       </c>
       <c r="T47">
-        <v>1.130115957583034</v>
+        <v>1.149245332075642</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.33022125139871</v>
+        <v>3.257825137237868</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07678469835459266</v>
+        <v>0.07683205517934534</v>
       </c>
       <c r="C48">
-        <v>242.4233433331375</v>
+        <v>236.4724759825305</v>
       </c>
       <c r="D48">
-        <v>451.1902165510165</v>
+        <v>450.501672531233</v>
       </c>
       <c r="E48">
-        <v>201.4345401355333</v>
+        <v>206.6968634663568</v>
       </c>
       <c r="F48">
-        <v>242.0668732178791</v>
+        <v>247.3291965487026</v>
       </c>
       <c r="G48">
         <v>33.3</v>
@@ -5223,28 +5223,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M48">
-        <v>15.51648657326605</v>
+        <v>15.85380149877184</v>
       </c>
       <c r="N48">
-        <v>35.03351342673396</v>
+        <v>34.69619850122817</v>
       </c>
       <c r="O48">
-        <v>5.114892960303158</v>
+        <v>5.065644981179313</v>
       </c>
       <c r="P48">
-        <v>29.9186204664308</v>
+        <v>29.63055352004886</v>
       </c>
       <c r="Q48">
-        <v>52.71862046643081</v>
+        <v>52.43055352004886</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09556232287887528</v>
+        <v>0.09642188147046289</v>
       </c>
       <c r="T48">
-        <v>1.149245332075642</v>
+        <v>1.169096569756649</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.257825137237868</v>
+        <v>3.188509708785999</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07683205517934534</v>
+        <v>0.07687941200409802</v>
       </c>
       <c r="C49">
-        <v>236.4724759825305</v>
+        <v>230.5237069508026</v>
       </c>
       <c r="D49">
-        <v>450.501672531233</v>
+        <v>449.8152268303286</v>
       </c>
       <c r="E49">
-        <v>206.6968634663568</v>
+        <v>211.9591867971802</v>
       </c>
       <c r="F49">
-        <v>247.3291965487026</v>
+        <v>252.591519879526</v>
       </c>
       <c r="G49">
         <v>33.3</v>
@@ -5305,28 +5305,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M49">
-        <v>15.85380149877184</v>
+        <v>16.19111642427762</v>
       </c>
       <c r="N49">
-        <v>34.69619850122817</v>
+        <v>34.35888357572239</v>
       </c>
       <c r="O49">
-        <v>5.065644981179313</v>
+        <v>5.016397002055469</v>
       </c>
       <c r="P49">
-        <v>29.63055352004886</v>
+        <v>29.34248657366692</v>
       </c>
       <c r="Q49">
-        <v>52.43055352004886</v>
+        <v>52.14248657366693</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09642188147046289</v>
+        <v>0.09731450000788081</v>
       </c>
       <c r="T49">
-        <v>1.169096569756649</v>
+        <v>1.189711316579233</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.188509708785999</v>
+        <v>3.122082423186291</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07687941200409802</v>
+        <v>0.07692676882885072</v>
       </c>
       <c r="C50">
-        <v>230.5237069508026</v>
+        <v>224.5770266606935</v>
       </c>
       <c r="D50">
-        <v>449.8152268303286</v>
+        <v>449.130869871043</v>
       </c>
       <c r="E50">
-        <v>211.9591867971802</v>
+        <v>217.2215101280037</v>
       </c>
       <c r="F50">
-        <v>252.591519879526</v>
+        <v>257.8538432103495</v>
       </c>
       <c r="G50">
         <v>33.3</v>
@@ -5387,28 +5387,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M50">
-        <v>16.19111642427762</v>
+        <v>16.5284313497834</v>
       </c>
       <c r="N50">
-        <v>34.35888357572239</v>
+        <v>34.02156865021661</v>
       </c>
       <c r="O50">
-        <v>5.016397002055469</v>
+        <v>4.967149022931625</v>
       </c>
       <c r="P50">
-        <v>29.34248657366692</v>
+        <v>29.05441962728498</v>
       </c>
       <c r="Q50">
-        <v>52.14248657366693</v>
+        <v>51.85441962728498</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09731450000788081</v>
+        <v>0.09824212319382492</v>
       </c>
       <c r="T50">
-        <v>1.189711316579233</v>
+        <v>1.211134484845841</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.122082423186291</v>
+        <v>3.058366455366162</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07692676882885072</v>
+        <v>0.08030472565360339</v>
       </c>
       <c r="C51">
-        <v>224.5770266606935</v>
+        <v>175.3455177082028</v>
       </c>
       <c r="D51">
-        <v>449.130869871043</v>
+        <v>405.1616842493757</v>
       </c>
       <c r="E51">
-        <v>217.2215101280037</v>
+        <v>222.4838334588271</v>
       </c>
       <c r="F51">
-        <v>257.8538432103495</v>
+        <v>263.1161665411729</v>
       </c>
       <c r="G51">
         <v>33.3</v>
@@ -5469,45 +5469,45 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M51">
-        <v>16.5284313497834</v>
+        <v>18.91805237431033</v>
       </c>
       <c r="N51">
-        <v>34.02156865021661</v>
+        <v>31.63194762568968</v>
       </c>
       <c r="O51">
-        <v>4.967149022931625</v>
+        <v>4.618264353350693</v>
       </c>
       <c r="P51">
-        <v>29.05441962728498</v>
+        <v>27.01368327233899</v>
       </c>
       <c r="Q51">
-        <v>51.85441962728498</v>
+        <v>49.81368327233899</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09824212319382492</v>
+        <v>0.09920685130720679</v>
       </c>
       <c r="T51">
-        <v>1.211134484845841</v>
+        <v>1.233414579843113</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.146</v>
       </c>
       <c r="W51">
-        <v>0.0547414</v>
+        <v>0.0614026</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.058366455366162</v>
+        <v>2.67205095957151</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08030472565360339</v>
+        <v>0.08041869447835609</v>
       </c>
       <c r="C52">
-        <v>175.3455177082028</v>
+        <v>168.7493543327296</v>
       </c>
       <c r="D52">
-        <v>405.1616842493757</v>
+        <v>403.8278442047259</v>
       </c>
       <c r="E52">
-        <v>222.4838334588271</v>
+        <v>227.7461567896506</v>
       </c>
       <c r="F52">
-        <v>263.1161665411729</v>
+        <v>268.3784898719964</v>
       </c>
       <c r="G52">
         <v>33.3</v>
@@ -5551,28 +5551,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M52">
-        <v>18.91805237431033</v>
+        <v>19.29641342179654</v>
       </c>
       <c r="N52">
-        <v>31.63194762568968</v>
+        <v>31.25358657820347</v>
       </c>
       <c r="O52">
-        <v>4.618264353350693</v>
+        <v>4.563023640417707</v>
       </c>
       <c r="P52">
-        <v>27.01368327233899</v>
+        <v>26.69056293778576</v>
       </c>
       <c r="Q52">
-        <v>49.81368327233899</v>
+        <v>49.49056293778577</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09920685130720679</v>
+        <v>0.1002109560782777</v>
       </c>
       <c r="T52">
-        <v>1.233414579843113</v>
+        <v>1.256604066472926</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.67205095957151</v>
+        <v>2.619657803501481</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08041869447835609</v>
+        <v>0.08053266330310876</v>
       </c>
       <c r="C53">
-        <v>168.7493543327296</v>
+        <v>162.1619444571521</v>
       </c>
       <c r="D53">
-        <v>403.8278442047259</v>
+        <v>402.5027576599719</v>
       </c>
       <c r="E53">
-        <v>227.7461567896506</v>
+        <v>233.008480120474</v>
       </c>
       <c r="F53">
-        <v>268.3784898719964</v>
+        <v>273.6408132028198</v>
       </c>
       <c r="G53">
         <v>33.3</v>
@@ -5633,28 +5633,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M53">
-        <v>19.29641342179654</v>
+        <v>19.67477446928275</v>
       </c>
       <c r="N53">
-        <v>31.25358657820347</v>
+        <v>30.87522553071727</v>
       </c>
       <c r="O53">
-        <v>4.563023640417707</v>
+        <v>4.507782927484721</v>
       </c>
       <c r="P53">
-        <v>26.69056293778576</v>
+        <v>26.36744260323255</v>
       </c>
       <c r="Q53">
-        <v>49.49056293778577</v>
+        <v>49.16744260323254</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1002109560782777</v>
+        <v>0.1012568985481433</v>
       </c>
       <c r="T53">
-        <v>1.256604066472926</v>
+        <v>1.280759781712315</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.619657803501481</v>
+        <v>2.56927976881876</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08053266330310876</v>
+        <v>0.08064663212786144</v>
       </c>
       <c r="C54">
-        <v>162.1619444571521</v>
+        <v>155.5832021943097</v>
       </c>
       <c r="D54">
-        <v>402.5027576599719</v>
+        <v>401.186338727953</v>
       </c>
       <c r="E54">
-        <v>233.008480120474</v>
+        <v>238.2708034512975</v>
       </c>
       <c r="F54">
-        <v>273.6408132028198</v>
+        <v>278.9031365336433</v>
       </c>
       <c r="G54">
         <v>33.3</v>
@@ -5715,28 +5715,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M54">
-        <v>19.67477446928275</v>
+        <v>20.05313551676895</v>
       </c>
       <c r="N54">
-        <v>30.87522553071727</v>
+        <v>30.49686448323106</v>
       </c>
       <c r="O54">
-        <v>4.507782927484721</v>
+        <v>4.452542214551734</v>
       </c>
       <c r="P54">
-        <v>26.36744260323255</v>
+        <v>26.04432226867932</v>
       </c>
       <c r="Q54">
-        <v>49.16744260323254</v>
+        <v>48.84432226867932</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1012568985481433</v>
+        <v>0.1023473492082158</v>
       </c>
       <c r="T54">
-        <v>1.280759781712315</v>
+        <v>1.305943399727849</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.56927976881876</v>
+        <v>2.520802792048594</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08064663212786144</v>
+        <v>0.08255912495261414</v>
       </c>
       <c r="C55">
-        <v>155.5832021943097</v>
+        <v>129.4480753025992</v>
       </c>
       <c r="D55">
-        <v>401.186338727953</v>
+        <v>380.313535167066</v>
       </c>
       <c r="E55">
-        <v>238.2708034512975</v>
+        <v>243.533126782121</v>
       </c>
       <c r="F55">
-        <v>278.9031365336433</v>
+        <v>284.1654598644668</v>
       </c>
       <c r="G55">
         <v>33.3</v>
@@ -5797,45 +5797,45 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M55">
-        <v>20.05313551676895</v>
+        <v>21.53974185772658</v>
       </c>
       <c r="N55">
-        <v>30.49686448323106</v>
+        <v>29.01025814227343</v>
       </c>
       <c r="O55">
-        <v>4.452542214551734</v>
+        <v>4.23549768877192</v>
       </c>
       <c r="P55">
-        <v>26.04432226867932</v>
+        <v>24.77476045350151</v>
       </c>
       <c r="Q55">
-        <v>48.84432226867932</v>
+        <v>47.57476045350151</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1023473492082158</v>
+        <v>0.1034852107665525</v>
       </c>
       <c r="T55">
-        <v>1.305943399727849</v>
+        <v>1.332221957657101</v>
       </c>
       <c r="U55">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.146</v>
       </c>
       <c r="W55">
-        <v>0.0614026</v>
+        <v>0.0647332</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.520802792048594</v>
+        <v>2.34682478248304</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08255912495261414</v>
+        <v>0.08270639977736682</v>
       </c>
       <c r="C56">
-        <v>129.4480753025992</v>
+        <v>122.6681124951354</v>
       </c>
       <c r="D56">
-        <v>380.313535167066</v>
+        <v>378.7958956904256</v>
       </c>
       <c r="E56">
-        <v>243.533126782121</v>
+        <v>248.7954501129444</v>
       </c>
       <c r="F56">
-        <v>284.1654598644668</v>
+        <v>289.4277831952902</v>
       </c>
       <c r="G56">
         <v>33.3</v>
@@ -5879,28 +5879,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M56">
-        <v>21.53974185772658</v>
+        <v>21.938625966203</v>
       </c>
       <c r="N56">
-        <v>29.01025814227343</v>
+        <v>28.61137403379701</v>
       </c>
       <c r="O56">
-        <v>4.23549768877192</v>
+        <v>4.177260608934364</v>
       </c>
       <c r="P56">
-        <v>24.77476045350151</v>
+        <v>24.43411342486265</v>
       </c>
       <c r="Q56">
-        <v>47.57476045350151</v>
+        <v>47.23411342486265</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1034852107665525</v>
+        <v>0.104673643949704</v>
       </c>
       <c r="T56">
-        <v>1.332221957657101</v>
+        <v>1.35966845149432</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.34682478248304</v>
+        <v>2.304155240983349</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08270639977736682</v>
+        <v>0.08285367460211951</v>
       </c>
       <c r="C57">
-        <v>122.6681124951354</v>
+        <v>115.9002138130443</v>
       </c>
       <c r="D57">
-        <v>378.7958956904256</v>
+        <v>377.2903203391579</v>
       </c>
       <c r="E57">
-        <v>248.7954501129444</v>
+        <v>254.0577734437679</v>
       </c>
       <c r="F57">
-        <v>289.4277831952902</v>
+        <v>294.6901065261137</v>
       </c>
       <c r="G57">
         <v>33.3</v>
@@ -5961,28 +5961,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M57">
-        <v>21.938625966203</v>
+        <v>22.33751007467942</v>
       </c>
       <c r="N57">
-        <v>28.61137403379701</v>
+        <v>28.21248992532059</v>
       </c>
       <c r="O57">
-        <v>4.177260608934364</v>
+        <v>4.119023529096807</v>
       </c>
       <c r="P57">
-        <v>24.43411342486265</v>
+        <v>24.09346639622379</v>
       </c>
       <c r="Q57">
-        <v>47.23411342486265</v>
+        <v>46.89346639622379</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.104673643949704</v>
+        <v>0.1059160968229989</v>
       </c>
       <c r="T57">
-        <v>1.35966845149432</v>
+        <v>1.38836251323323</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.304155240983349</v>
+        <v>2.263009611680074</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08285367460211951</v>
+        <v>0.08300094942687218</v>
       </c>
       <c r="C58">
-        <v>115.9002138130443</v>
+        <v>109.1442359743417</v>
       </c>
       <c r="D58">
-        <v>377.2903203391579</v>
+        <v>375.7966658312789</v>
       </c>
       <c r="E58">
-        <v>254.0577734437679</v>
+        <v>259.3200967745914</v>
       </c>
       <c r="F58">
-        <v>294.6901065261137</v>
+        <v>299.9524298569372</v>
       </c>
       <c r="G58">
         <v>33.3</v>
@@ -6043,28 +6043,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M58">
-        <v>22.33751007467942</v>
+        <v>22.73639418315584</v>
       </c>
       <c r="N58">
-        <v>28.21248992532059</v>
+        <v>27.81360581684417</v>
       </c>
       <c r="O58">
-        <v>4.119023529096807</v>
+        <v>4.060786449259249</v>
       </c>
       <c r="P58">
-        <v>24.09346639622379</v>
+        <v>23.75281936758493</v>
       </c>
       <c r="Q58">
-        <v>46.89346639622379</v>
+        <v>46.55281936758493</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1059160968229989</v>
+        <v>0.1072163382020283</v>
       </c>
       <c r="T58">
-        <v>1.38836251323323</v>
+        <v>1.418391182494881</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.263009611680074</v>
+        <v>2.223307688668143</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08300094942687218</v>
+        <v>0.08314822425162488</v>
       </c>
       <c r="C59">
-        <v>109.1442359743417</v>
+        <v>102.4000379570519</v>
       </c>
       <c r="D59">
-        <v>375.7966658312789</v>
+        <v>374.3147911448125</v>
       </c>
       <c r="E59">
-        <v>259.3200967745914</v>
+        <v>264.5824201054148</v>
       </c>
       <c r="F59">
-        <v>299.9524298569372</v>
+        <v>305.2147531877606</v>
       </c>
       <c r="G59">
         <v>33.3</v>
@@ -6125,28 +6125,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M59">
-        <v>22.73639418315584</v>
+        <v>23.13527829163226</v>
       </c>
       <c r="N59">
-        <v>27.81360581684417</v>
+        <v>27.41472170836775</v>
       </c>
       <c r="O59">
-        <v>4.060786449259249</v>
+        <v>4.002549369421692</v>
       </c>
       <c r="P59">
-        <v>23.75281936758493</v>
+        <v>23.41217233894606</v>
       </c>
       <c r="Q59">
-        <v>46.55281936758493</v>
+        <v>46.21217233894606</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1072163382020283</v>
+        <v>0.1085784958372021</v>
       </c>
       <c r="T59">
-        <v>1.418391182494881</v>
+        <v>1.449849788388039</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.223307688668143</v>
+        <v>2.184974797484209</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08314822425162487</v>
+        <v>0.08329549907637755</v>
       </c>
       <c r="C60">
-        <v>102.4000379570521</v>
+        <v>95.66748095482455</v>
       </c>
       <c r="D60">
-        <v>374.3147911448127</v>
+        <v>372.8445574734085</v>
       </c>
       <c r="E60">
-        <v>264.5824201054148</v>
+        <v>269.8447434362382</v>
       </c>
       <c r="F60">
-        <v>305.2147531877606</v>
+        <v>310.477076518584</v>
       </c>
       <c r="G60">
         <v>33.3</v>
@@ -6207,28 +6207,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M60">
-        <v>23.13527829163225</v>
+        <v>23.53416240010867</v>
       </c>
       <c r="N60">
-        <v>27.41472170836776</v>
+        <v>27.01583759989134</v>
       </c>
       <c r="O60">
-        <v>4.002549369421692</v>
+        <v>3.944312289584135</v>
       </c>
       <c r="P60">
-        <v>23.41217233894607</v>
+        <v>23.07152531030721</v>
       </c>
       <c r="Q60">
-        <v>46.21217233894607</v>
+        <v>45.87152531030721</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1085784958372021</v>
+        <v>0.1100071001862867</v>
       </c>
       <c r="T60">
-        <v>1.449849788388039</v>
+        <v>1.482842960422326</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.18497479748421</v>
+        <v>2.147941326340409</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08329549907637755</v>
+        <v>0.08344277390113024</v>
       </c>
       <c r="C61">
-        <v>95.66748095482455</v>
+        <v>88.94642833359035</v>
       </c>
       <c r="D61">
-        <v>372.8445574734085</v>
+        <v>371.3858281829978</v>
       </c>
       <c r="E61">
-        <v>269.8447434362382</v>
+        <v>275.1070667670617</v>
       </c>
       <c r="F61">
-        <v>310.477076518584</v>
+        <v>315.7393998494074</v>
       </c>
       <c r="G61">
         <v>33.3</v>
@@ -6289,28 +6289,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M61">
-        <v>23.53416240010867</v>
+        <v>23.93304650858509</v>
       </c>
       <c r="N61">
-        <v>27.01583759989134</v>
+        <v>26.61695349141493</v>
       </c>
       <c r="O61">
-        <v>3.944312289584135</v>
+        <v>3.886075209746579</v>
       </c>
       <c r="P61">
-        <v>23.07152531030721</v>
+        <v>22.73087828166835</v>
       </c>
       <c r="Q61">
-        <v>45.87152531030721</v>
+        <v>45.53087828166835</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1100071001862867</v>
+        <v>0.1115071347528256</v>
       </c>
       <c r="T61">
-        <v>1.482842960422326</v>
+        <v>1.517485791058328</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.147941326340409</v>
+        <v>2.112142304234736</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08344277390113024</v>
+        <v>0.08359004872588294</v>
       </c>
       <c r="C62">
-        <v>88.94642833359035</v>
+        <v>82.23674558923364</v>
       </c>
       <c r="D62">
-        <v>371.3858281829978</v>
+        <v>369.9384687694646</v>
       </c>
       <c r="E62">
-        <v>275.1070667670617</v>
+        <v>280.3693900978852</v>
       </c>
       <c r="F62">
-        <v>315.7393998494074</v>
+        <v>321.001723180231</v>
       </c>
       <c r="G62">
         <v>33.3</v>
@@ -6371,28 +6371,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M62">
-        <v>23.93304650858509</v>
+        <v>24.33193061706151</v>
       </c>
       <c r="N62">
-        <v>26.61695349141493</v>
+        <v>26.2180693829385</v>
       </c>
       <c r="O62">
-        <v>3.886075209746579</v>
+        <v>3.827838129909021</v>
       </c>
       <c r="P62">
-        <v>22.73087828166835</v>
+        <v>22.39023125302948</v>
       </c>
       <c r="Q62">
-        <v>45.53087828166835</v>
+        <v>45.19023125302948</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1115071347528256</v>
+        <v>0.1130840941689306</v>
       </c>
       <c r="T62">
-        <v>1.517485791058328</v>
+        <v>1.553905177111561</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.112142304234736</v>
+        <v>2.077517020558757</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08359004872588294</v>
+        <v>0.08373732355063562</v>
       </c>
       <c r="C63">
-        <v>82.23674558923364</v>
+        <v>75.5383003062492</v>
       </c>
       <c r="D63">
-        <v>369.9384687694646</v>
+        <v>368.5023468173036</v>
       </c>
       <c r="E63">
-        <v>280.3693900978852</v>
+        <v>285.6317134287086</v>
       </c>
       <c r="F63">
-        <v>321.001723180231</v>
+        <v>326.2640465110544</v>
       </c>
       <c r="G63">
         <v>33.3</v>
@@ -6453,28 +6453,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M63">
-        <v>24.33193061706151</v>
+        <v>24.73081472553793</v>
       </c>
       <c r="N63">
-        <v>26.2180693829385</v>
+        <v>25.81918527446209</v>
       </c>
       <c r="O63">
-        <v>3.827838129909021</v>
+        <v>3.769601050071465</v>
       </c>
       <c r="P63">
-        <v>22.39023125302948</v>
+        <v>22.04958422439062</v>
       </c>
       <c r="Q63">
-        <v>45.19023125302948</v>
+        <v>44.84958422439063</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1130840941689306</v>
+        <v>0.1147440514490411</v>
       </c>
       <c r="T63">
-        <v>1.553905177111561</v>
+        <v>1.592241372957069</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.077517020558757</v>
+        <v>2.044008681517486</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08373732355063562</v>
+        <v>0.08388459837538831</v>
       </c>
       <c r="C64">
-        <v>75.5383003062492</v>
+        <v>68.85096211735799</v>
       </c>
       <c r="D64">
-        <v>368.5023468173036</v>
+        <v>367.0773319592358</v>
       </c>
       <c r="E64">
-        <v>285.6317134287086</v>
+        <v>290.8940367595321</v>
       </c>
       <c r="F64">
-        <v>326.2640465110544</v>
+        <v>331.5263698418779</v>
       </c>
       <c r="G64">
         <v>33.3</v>
@@ -6535,28 +6535,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M64">
-        <v>24.73081472553793</v>
+        <v>25.12969883401435</v>
       </c>
       <c r="N64">
-        <v>25.81918527446209</v>
+        <v>25.42030116598567</v>
       </c>
       <c r="O64">
-        <v>3.769601050071465</v>
+        <v>3.711363970233907</v>
       </c>
       <c r="P64">
-        <v>22.04958422439062</v>
+        <v>21.70893719575176</v>
       </c>
       <c r="Q64">
-        <v>44.84958422439063</v>
+        <v>44.50893719575176</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1147440514490411</v>
+        <v>0.1164937361496981</v>
       </c>
       <c r="T64">
-        <v>1.592241372957069</v>
+        <v>1.632649795605037</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.044008681517486</v>
+        <v>2.011564099271177</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08388459837538831</v>
+        <v>0.09179302520014099</v>
       </c>
       <c r="C65">
-        <v>68.85096211735799</v>
+        <v>0.470281031364209</v>
       </c>
       <c r="D65">
-        <v>367.0773319592358</v>
+        <v>303.9589742040655</v>
       </c>
       <c r="E65">
-        <v>290.8940367595321</v>
+        <v>296.1563600903555</v>
       </c>
       <c r="F65">
-        <v>331.5263698418779</v>
+        <v>336.7886931727013</v>
       </c>
       <c r="G65">
         <v>33.3</v>
@@ -6617,45 +6617,45 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M65">
-        <v>25.12969883401435</v>
+        <v>30.31098238554312</v>
       </c>
       <c r="N65">
-        <v>25.42030116598567</v>
+        <v>20.23901761445689</v>
       </c>
       <c r="O65">
-        <v>3.711363970233907</v>
+        <v>2.954896571710707</v>
       </c>
       <c r="P65">
-        <v>21.70893719575176</v>
+        <v>17.28412104274619</v>
       </c>
       <c r="Q65">
-        <v>44.50893719575176</v>
+        <v>40.08412104274619</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1164937361496981</v>
+        <v>0.1183406255559472</v>
       </c>
       <c r="T65">
-        <v>1.632649795605037</v>
+        <v>1.675303130622337</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V65">
         <v>0.146</v>
       </c>
       <c r="W65">
-        <v>0.0647332</v>
+        <v>0.07686</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.011564099271177</v>
+        <v>1.66771236105201</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09179302520014099</v>
+        <v>0.09206156802489368</v>
       </c>
       <c r="C66">
-        <v>0.470281031364209</v>
+        <v>-6.556487497204557</v>
       </c>
       <c r="D66">
-        <v>303.9589742040655</v>
+        <v>302.1945290063202</v>
       </c>
       <c r="E66">
-        <v>296.1563600903555</v>
+        <v>301.418683421179</v>
       </c>
       <c r="F66">
-        <v>336.7886931727013</v>
+        <v>342.0510165035248</v>
       </c>
       <c r="G66">
         <v>33.3</v>
@@ -6699,28 +6699,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M66">
-        <v>30.31098238554312</v>
+        <v>30.78459148531723</v>
       </c>
       <c r="N66">
-        <v>20.23901761445689</v>
+        <v>19.76540851468278</v>
       </c>
       <c r="O66">
-        <v>2.954896571710707</v>
+        <v>2.885749643143686</v>
       </c>
       <c r="P66">
-        <v>17.28412104274619</v>
+        <v>16.87965887153909</v>
       </c>
       <c r="Q66">
-        <v>40.08412104274619</v>
+        <v>39.67965887153909</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1183406255559472</v>
+        <v>0.1202930514996962</v>
       </c>
       <c r="T66">
-        <v>1.675303130622337</v>
+        <v>1.720393799069196</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.66771236105201</v>
+        <v>1.642055247805056</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09206156802489368</v>
+        <v>0.09233011084964635</v>
       </c>
       <c r="C67">
-        <v>-6.556487497204557</v>
+        <v>-13.56288946790897</v>
       </c>
       <c r="D67">
-        <v>302.1945290063202</v>
+        <v>300.4504503664393</v>
       </c>
       <c r="E67">
-        <v>301.418683421179</v>
+        <v>306.6810067520025</v>
       </c>
       <c r="F67">
-        <v>342.0510165035248</v>
+        <v>347.3133398343483</v>
       </c>
       <c r="G67">
         <v>33.3</v>
@@ -6781,28 +6781,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M67">
-        <v>30.78459148531723</v>
+        <v>31.25820058509134</v>
       </c>
       <c r="N67">
-        <v>19.76540851468278</v>
+        <v>19.29179941490867</v>
       </c>
       <c r="O67">
-        <v>2.885749643143686</v>
+        <v>2.816602714576666</v>
       </c>
       <c r="P67">
-        <v>16.87965887153909</v>
+        <v>16.47519670033201</v>
       </c>
       <c r="Q67">
-        <v>39.67965887153909</v>
+        <v>39.275196700332</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1202930514996962</v>
+        <v>0.1223603260283716</v>
       </c>
       <c r="T67">
-        <v>1.720393799069196</v>
+        <v>1.768136859777636</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.642055247805056</v>
+        <v>1.617175622838313</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09233011084964635</v>
+        <v>0.09259865367439904</v>
       </c>
       <c r="C68">
-        <v>-13.56288946790897</v>
+        <v>-20.54927548653916</v>
       </c>
       <c r="D68">
-        <v>300.4504503664393</v>
+        <v>298.7263876786325</v>
       </c>
       <c r="E68">
-        <v>306.6810067520025</v>
+        <v>311.9433300828259</v>
       </c>
       <c r="F68">
-        <v>347.3133398343483</v>
+        <v>352.5756631651717</v>
       </c>
       <c r="G68">
         <v>33.3</v>
@@ -6863,28 +6863,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M68">
-        <v>31.25820058509134</v>
+        <v>31.73180968486545</v>
       </c>
       <c r="N68">
-        <v>19.29179941490867</v>
+        <v>18.81819031513456</v>
       </c>
       <c r="O68">
-        <v>2.816602714576666</v>
+        <v>2.747455786009645</v>
       </c>
       <c r="P68">
-        <v>16.47519670033201</v>
+        <v>16.07073452912491</v>
       </c>
       <c r="Q68">
-        <v>39.275196700332</v>
+        <v>38.87073452912492</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1223603260283716</v>
+        <v>0.1245528899224213</v>
       </c>
       <c r="T68">
-        <v>1.768136859777636</v>
+        <v>1.81877343931689</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.617175622838313</v>
+        <v>1.593038673243711</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09259865367439904</v>
+        <v>0.09286719649915172</v>
       </c>
       <c r="C69">
-        <v>-20.54927548653916</v>
+        <v>-27.51598815733166</v>
       </c>
       <c r="D69">
-        <v>298.7263876786325</v>
+        <v>297.0219983386635</v>
       </c>
       <c r="E69">
-        <v>311.9433300828259</v>
+        <v>317.2056534136494</v>
       </c>
       <c r="F69">
-        <v>352.5756631651717</v>
+        <v>357.8379864959952</v>
       </c>
       <c r="G69">
         <v>33.3</v>
@@ -6945,28 +6945,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M69">
-        <v>31.73180968486545</v>
+        <v>32.20541878463956</v>
       </c>
       <c r="N69">
-        <v>18.81819031513456</v>
+        <v>18.34458121536045</v>
       </c>
       <c r="O69">
-        <v>2.747455786009645</v>
+        <v>2.678308857442625</v>
       </c>
       <c r="P69">
-        <v>16.07073452912491</v>
+        <v>15.66627235791782</v>
       </c>
       <c r="Q69">
-        <v>38.87073452912492</v>
+        <v>38.46627235791782</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1245528899224213</v>
+        <v>0.1268824890598491</v>
       </c>
       <c r="T69">
-        <v>1.81877343931689</v>
+        <v>1.872574805077347</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.593038673243711</v>
+        <v>1.569611633931304</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09286719649915172</v>
+        <v>0.09313573932390441</v>
       </c>
       <c r="C70">
-        <v>-27.51598815733166</v>
+        <v>-34.46336230994035</v>
       </c>
       <c r="D70">
-        <v>297.0219983386635</v>
+        <v>295.3369475168783</v>
       </c>
       <c r="E70">
-        <v>317.2056534136494</v>
+        <v>322.4679767444729</v>
       </c>
       <c r="F70">
-        <v>357.8379864959952</v>
+        <v>363.1003098268187</v>
       </c>
       <c r="G70">
         <v>33.3</v>
@@ -7027,28 +7027,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M70">
-        <v>32.20541878463956</v>
+        <v>32.67902788441368</v>
       </c>
       <c r="N70">
-        <v>18.34458121536045</v>
+        <v>17.87097211558633</v>
       </c>
       <c r="O70">
-        <v>2.678308857442625</v>
+        <v>2.609161928875605</v>
       </c>
       <c r="P70">
-        <v>15.66627235791782</v>
+        <v>15.26181018671073</v>
       </c>
       <c r="Q70">
-        <v>38.46627235791782</v>
+        <v>38.06181018671073</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1268824890598491</v>
+        <v>0.1293623849158207</v>
       </c>
       <c r="T70">
-        <v>1.872574805077347</v>
+        <v>1.929847226693319</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.569611633931304</v>
+        <v>1.546863639236647</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09313573932390441</v>
+        <v>0.09340428214865709</v>
       </c>
       <c r="C71">
-        <v>-34.46336230994035</v>
+        <v>-41.39172521872337</v>
       </c>
       <c r="D71">
-        <v>295.3369475168783</v>
+        <v>293.6709079389187</v>
       </c>
       <c r="E71">
-        <v>322.4679767444729</v>
+        <v>327.7303000752963</v>
       </c>
       <c r="F71">
-        <v>363.1003098268187</v>
+        <v>368.3626331576421</v>
       </c>
       <c r="G71">
         <v>33.3</v>
@@ -7109,28 +7109,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M71">
-        <v>32.67902788441368</v>
+        <v>33.15263698418779</v>
       </c>
       <c r="N71">
-        <v>17.87097211558633</v>
+        <v>17.39736301581222</v>
       </c>
       <c r="O71">
-        <v>2.609161928875605</v>
+        <v>2.540015000308585</v>
       </c>
       <c r="P71">
-        <v>15.26181018671073</v>
+        <v>14.85734801550364</v>
       </c>
       <c r="Q71">
-        <v>38.06181018671073</v>
+        <v>37.65734801550364</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1293623849158207</v>
+        <v>0.1320076071621903</v>
       </c>
       <c r="T71">
-        <v>1.929847226693319</v>
+        <v>1.990937809750354</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.546863639236647</v>
+        <v>1.524765587247552</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09340428214865709</v>
+        <v>0.09367282497340979</v>
       </c>
       <c r="C72">
-        <v>-41.39172521872337</v>
+        <v>-48.30139681465147</v>
       </c>
       <c r="D72">
-        <v>293.6709079389187</v>
+        <v>292.0235596738141</v>
       </c>
       <c r="E72">
-        <v>327.7303000752963</v>
+        <v>332.9926234061198</v>
       </c>
       <c r="F72">
-        <v>368.3626331576421</v>
+        <v>373.6249564884656</v>
       </c>
       <c r="G72">
         <v>33.3</v>
@@ -7191,28 +7191,28 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M72">
-        <v>33.15263698418779</v>
+        <v>33.6262460839619</v>
       </c>
       <c r="N72">
-        <v>17.39736301581222</v>
+        <v>16.92375391603811</v>
       </c>
       <c r="O72">
-        <v>2.540015000308585</v>
+        <v>2.470868071741564</v>
       </c>
       <c r="P72">
-        <v>14.85734801550364</v>
+        <v>14.45288584429655</v>
       </c>
       <c r="Q72">
-        <v>37.65734801550364</v>
+        <v>37.25288584429654</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1320076071621903</v>
+        <v>0.1348352585289992</v>
       </c>
       <c r="T72">
-        <v>1.990937809750354</v>
+        <v>2.056241536466496</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.524765587247552</v>
+        <v>1.503290015596178</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09367282497340979</v>
+        <v>0.1305494319536089</v>
       </c>
       <c r="C73">
-        <v>-48.30139681465141</v>
+        <v>-180.6305073888953</v>
       </c>
       <c r="D73">
-        <v>292.0235596738141</v>
+        <v>164.9567724303937</v>
       </c>
       <c r="E73">
-        <v>332.9926234061197</v>
+        <v>338.2549467369432</v>
       </c>
       <c r="F73">
-        <v>373.6249564884655</v>
+        <v>378.8872798192889</v>
       </c>
       <c r="G73">
         <v>33.3</v>
@@ -7273,45 +7273,45 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M73">
-        <v>33.6262460839619</v>
+        <v>55.62065267747163</v>
       </c>
       <c r="N73">
-        <v>16.92375391603812</v>
+        <v>-5.070652677471614</v>
       </c>
       <c r="O73">
-        <v>2.470868071741565</v>
+        <v>-0.7403152909108556</v>
       </c>
       <c r="P73">
-        <v>14.45288584429655</v>
+        <v>-4.330337386560759</v>
       </c>
       <c r="Q73">
-        <v>37.25288584429655</v>
+        <v>18.46966261343924</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1348352585289992</v>
+        <v>0.1388508065182565</v>
       </c>
       <c r="T73">
-        <v>2.056241536466495</v>
+        <v>2.148979365317701</v>
       </c>
       <c r="U73">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.146</v>
+        <v>0.1326899208248466</v>
       </c>
       <c r="W73">
-        <v>0.07686</v>
+        <v>0.1273211196229125</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.503290015596178</v>
+        <v>0.9088350741427849</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1305494319536089</v>
+        <v>0.1315594319536088</v>
       </c>
       <c r="C74">
-        <v>-180.6305073888953</v>
+        <v>-187.8355481137055</v>
       </c>
       <c r="D74">
-        <v>164.9567724303937</v>
+        <v>163.014055036407</v>
       </c>
       <c r="E74">
-        <v>338.2549467369432</v>
+        <v>343.5172700677667</v>
       </c>
       <c r="F74">
-        <v>378.8872798192889</v>
+        <v>384.1496031501125</v>
       </c>
       <c r="G74">
         <v>33.3</v>
@@ -7355,37 +7355,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M74">
-        <v>55.62065267747163</v>
+        <v>56.39316174243651</v>
       </c>
       <c r="N74">
-        <v>-5.070652677471614</v>
+        <v>-5.8431617424365</v>
       </c>
       <c r="O74">
-        <v>-0.7403152909108556</v>
+        <v>-0.853101614395729</v>
       </c>
       <c r="P74">
-        <v>-4.330337386560759</v>
+        <v>-4.990060128040771</v>
       </c>
       <c r="Q74">
-        <v>18.46966261343924</v>
+        <v>17.80993987195923</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1388508065182565</v>
+        <v>0.1422971326855993</v>
       </c>
       <c r="T74">
-        <v>2.148979365317701</v>
+        <v>2.228571193662801</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1326899208248466</v>
+        <v>0.130872250676561</v>
       </c>
       <c r="W74">
-        <v>0.1273211196229125</v>
+        <v>0.1275879536006808</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9088350741427849</v>
+        <v>0.8963852786065823</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1315594319536088</v>
+        <v>0.1325694319536088</v>
       </c>
       <c r="C75">
-        <v>-187.8355481137055</v>
+        <v>-194.9953622068841</v>
       </c>
       <c r="D75">
-        <v>163.014055036407</v>
+        <v>161.1165642740519</v>
       </c>
       <c r="E75">
-        <v>343.5172700677667</v>
+        <v>348.7795933985901</v>
       </c>
       <c r="F75">
-        <v>384.1496031501125</v>
+        <v>389.4119264809359</v>
       </c>
       <c r="G75">
         <v>33.3</v>
@@ -7437,37 +7437,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M75">
-        <v>56.39316174243651</v>
+        <v>57.1656708074014</v>
       </c>
       <c r="N75">
-        <v>-5.8431617424365</v>
+        <v>-6.615670807401386</v>
       </c>
       <c r="O75">
-        <v>-0.853101614395729</v>
+        <v>-0.9658879378806023</v>
       </c>
       <c r="P75">
-        <v>-4.990060128040771</v>
+        <v>-5.649782869520784</v>
       </c>
       <c r="Q75">
-        <v>17.80993987195923</v>
+        <v>17.15021713047922</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1422971326855993</v>
+        <v>0.1460085608658146</v>
       </c>
       <c r="T75">
-        <v>2.228571193662801</v>
+        <v>2.314285470342139</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.130872250676561</v>
+        <v>0.1291037067484994</v>
       </c>
       <c r="W75">
-        <v>0.1275879536006808</v>
+        <v>0.1278475758493203</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8963852786065823</v>
+        <v>0.8842719640308176</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1325694319536088</v>
+        <v>0.1335794319536088</v>
       </c>
       <c r="C76">
-        <v>-194.9953622068841</v>
+        <v>-202.1115108165358</v>
       </c>
       <c r="D76">
-        <v>161.1165642740519</v>
+        <v>159.2627389952235</v>
       </c>
       <c r="E76">
-        <v>348.7795933985901</v>
+        <v>354.0419167294136</v>
       </c>
       <c r="F76">
-        <v>389.4119264809359</v>
+        <v>394.6742498117594</v>
       </c>
       <c r="G76">
         <v>33.3</v>
@@ -7519,37 +7519,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M76">
-        <v>57.1656708074014</v>
+        <v>57.93817987236628</v>
       </c>
       <c r="N76">
-        <v>-6.615670807401386</v>
+        <v>-7.388179872366265</v>
       </c>
       <c r="O76">
-        <v>-0.9658879378806023</v>
+        <v>-1.078674261365475</v>
       </c>
       <c r="P76">
-        <v>-5.649782869520784</v>
+        <v>-6.309505611000791</v>
       </c>
       <c r="Q76">
-        <v>17.15021713047922</v>
+        <v>16.49049438899921</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1460085608658146</v>
+        <v>0.1500169033004472</v>
       </c>
       <c r="T76">
-        <v>2.314285470342139</v>
+        <v>2.406856889155825</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1291037067484994</v>
+        <v>0.1273823239918527</v>
       </c>
       <c r="W76">
-        <v>0.1278475758493203</v>
+        <v>0.128100274837996</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8842719640308176</v>
+        <v>0.8724816711770735</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1335794319536088</v>
+        <v>0.1345894319536088</v>
       </c>
       <c r="C77">
-        <v>-202.1115108165358</v>
+        <v>-209.1854840571056</v>
       </c>
       <c r="D77">
-        <v>159.2627389952235</v>
+        <v>157.4510890854772</v>
       </c>
       <c r="E77">
-        <v>354.0419167294136</v>
+        <v>359.304240060237</v>
       </c>
       <c r="F77">
-        <v>394.6742498117594</v>
+        <v>399.9365731425828</v>
       </c>
       <c r="G77">
         <v>33.3</v>
@@ -7601,37 +7601,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M77">
-        <v>57.93817987236628</v>
+        <v>58.71068893733116</v>
       </c>
       <c r="N77">
-        <v>-7.388179872366265</v>
+        <v>-8.160688937331152</v>
       </c>
       <c r="O77">
-        <v>-1.078674261365475</v>
+        <v>-1.191460584850348</v>
       </c>
       <c r="P77">
-        <v>-6.309505611000791</v>
+        <v>-6.969228352480804</v>
       </c>
       <c r="Q77">
-        <v>16.49049438899921</v>
+        <v>15.8307716475192</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1500169033004472</v>
+        <v>0.1543592742712992</v>
       </c>
       <c r="T77">
-        <v>2.406856889155825</v>
+        <v>2.507142592870652</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1273823239918527</v>
+        <v>0.1257062407814336</v>
       </c>
       <c r="W77">
-        <v>0.128100274837996</v>
+        <v>0.1283463238532856</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8724816711770735</v>
+        <v>0.8610016491879015</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1345894319536088</v>
+        <v>0.1355994319536089</v>
       </c>
       <c r="C78">
-        <v>-209.1854840571056</v>
+        <v>-216.2187050040574</v>
       </c>
       <c r="D78">
-        <v>157.4510890854772</v>
+        <v>155.6801914693488</v>
       </c>
       <c r="E78">
-        <v>359.304240060237</v>
+        <v>364.5665633910605</v>
       </c>
       <c r="F78">
-        <v>399.9365731425828</v>
+        <v>405.1988964734063</v>
       </c>
       <c r="G78">
         <v>33.3</v>
@@ -7683,37 +7683,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M78">
-        <v>58.71068893733116</v>
+        <v>59.48319800229604</v>
       </c>
       <c r="N78">
-        <v>-8.160688937331152</v>
+        <v>-8.933198002296031</v>
       </c>
       <c r="O78">
-        <v>-1.191460584850348</v>
+        <v>-1.30424690833522</v>
       </c>
       <c r="P78">
-        <v>-6.969228352480804</v>
+        <v>-7.628951093960811</v>
       </c>
       <c r="Q78">
-        <v>15.8307716475192</v>
+        <v>15.17104890603919</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1543592742712992</v>
+        <v>0.1590792427178774</v>
       </c>
       <c r="T78">
-        <v>2.507142592870652</v>
+        <v>2.61614879256068</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1257062407814336</v>
+        <v>0.1240736921998565</v>
       </c>
       <c r="W78">
-        <v>0.1283463238532856</v>
+        <v>0.1285859819850611</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8610016491879015</v>
+        <v>0.8498198095880586</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1355994319536089</v>
+        <v>0.1366094319536088</v>
       </c>
       <c r="C79">
-        <v>-216.2187050040574</v>
+        <v>-223.2125334219777</v>
       </c>
       <c r="D79">
-        <v>155.6801914693488</v>
+        <v>153.9486863822521</v>
       </c>
       <c r="E79">
-        <v>364.5665633910605</v>
+        <v>369.828886721884</v>
       </c>
       <c r="F79">
-        <v>405.1988964734063</v>
+        <v>410.4612198042298</v>
       </c>
       <c r="G79">
         <v>33.3</v>
@@ -7765,37 +7765,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M79">
-        <v>59.48319800229604</v>
+        <v>60.25570706726094</v>
       </c>
       <c r="N79">
-        <v>-8.933198002296031</v>
+        <v>-9.705707067260924</v>
       </c>
       <c r="O79">
-        <v>-1.30424690833522</v>
+        <v>-1.417033231820095</v>
       </c>
       <c r="P79">
-        <v>-7.628951093960811</v>
+        <v>-8.288673835440829</v>
       </c>
       <c r="Q79">
-        <v>15.17104890603919</v>
+        <v>14.51132616455917</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1590792427178774</v>
+        <v>0.1642282992050537</v>
       </c>
       <c r="T79">
-        <v>2.61614879256068</v>
+        <v>2.735064646767984</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1240736921998565</v>
+        <v>0.1224830038383199</v>
       </c>
       <c r="W79">
-        <v>0.1285859819850611</v>
+        <v>0.1288194950365346</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8498198095880586</v>
+        <v>0.838924683824109</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1366094319536088</v>
+        <v>0.1376194319536088</v>
       </c>
       <c r="C80">
-        <v>-223.2125334219777</v>
+        <v>-230.1682692466253</v>
       </c>
       <c r="D80">
-        <v>153.9486863822521</v>
+        <v>152.2552738884279</v>
       </c>
       <c r="E80">
-        <v>369.828886721884</v>
+        <v>375.0912100527074</v>
       </c>
       <c r="F80">
-        <v>410.4612198042298</v>
+        <v>415.7235431350532</v>
       </c>
       <c r="G80">
         <v>33.3</v>
@@ -7847,37 +7847,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M80">
-        <v>60.25570706726094</v>
+        <v>61.02821613222581</v>
       </c>
       <c r="N80">
-        <v>-9.705707067260924</v>
+        <v>-10.4782161322258</v>
       </c>
       <c r="O80">
-        <v>-1.417033231820095</v>
+        <v>-1.529819555304967</v>
       </c>
       <c r="P80">
-        <v>-8.288673835440829</v>
+        <v>-8.948396576920835</v>
       </c>
       <c r="Q80">
-        <v>14.51132616455917</v>
+        <v>13.85160342307917</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1642282992050537</v>
+        <v>0.169867742024342</v>
       </c>
       <c r="T80">
-        <v>2.735064646767984</v>
+        <v>2.865305820423602</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1224830038383199</v>
+        <v>0.1209325860682146</v>
       </c>
       <c r="W80">
-        <v>0.1288194950365346</v>
+        <v>0.1290470963651861</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.838924683824109</v>
+        <v>0.8283053840288672</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1376194319536088</v>
+        <v>0.1386294319536089</v>
       </c>
       <c r="C81">
-        <v>-230.1682692466253</v>
+        <v>-237.0871558396711</v>
       </c>
       <c r="D81">
-        <v>152.2552738884279</v>
+        <v>150.5987106262056</v>
       </c>
       <c r="E81">
-        <v>375.0912100527074</v>
+        <v>380.3535333835309</v>
       </c>
       <c r="F81">
-        <v>415.7235431350532</v>
+        <v>420.9858664658767</v>
       </c>
       <c r="G81">
         <v>33.3</v>
@@ -7929,37 +7929,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M81">
-        <v>61.02821613222581</v>
+        <v>61.8007251971907</v>
       </c>
       <c r="N81">
-        <v>-10.4782161322258</v>
+        <v>-11.25072519719069</v>
       </c>
       <c r="O81">
-        <v>-1.529819555304967</v>
+        <v>-1.642605878789841</v>
       </c>
       <c r="P81">
-        <v>-8.948396576920835</v>
+        <v>-9.608119318400849</v>
       </c>
       <c r="Q81">
-        <v>13.85160342307917</v>
+        <v>13.19188068159915</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.169867742024342</v>
+        <v>0.1760711291255591</v>
       </c>
       <c r="T81">
-        <v>2.865305820423602</v>
+        <v>3.008571111444783</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1209325860682146</v>
+        <v>0.1194209287423619</v>
       </c>
       <c r="W81">
-        <v>0.1290470963651861</v>
+        <v>0.1292690076606213</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8283053840288672</v>
+        <v>0.8179515667285063</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1386294319536089</v>
+        <v>0.1396394319536088</v>
       </c>
       <c r="C82">
-        <v>-237.0871558396711</v>
+        <v>-243.9703830332508</v>
       </c>
       <c r="D82">
-        <v>150.5987106262056</v>
+        <v>148.9778067634493</v>
       </c>
       <c r="E82">
-        <v>380.3535333835309</v>
+        <v>385.6158567143543</v>
       </c>
       <c r="F82">
-        <v>420.9858664658767</v>
+        <v>426.2481897967001</v>
       </c>
       <c r="G82">
         <v>33.3</v>
@@ -8011,37 +8011,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M82">
-        <v>61.8007251971907</v>
+        <v>62.57323426215558</v>
       </c>
       <c r="N82">
-        <v>-11.25072519719069</v>
+        <v>-12.02323426215557</v>
       </c>
       <c r="O82">
-        <v>-1.642605878789841</v>
+        <v>-1.755392202274713</v>
       </c>
       <c r="P82">
-        <v>-9.608119318400849</v>
+        <v>-10.26784205988086</v>
       </c>
       <c r="Q82">
-        <v>13.19188068159915</v>
+        <v>12.53215794011914</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1760711291255591</v>
+        <v>0.1829275043426938</v>
       </c>
       <c r="T82">
-        <v>3.008571111444783</v>
+        <v>3.166916959415561</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1194209287423619</v>
+        <v>0.1179465962887525</v>
       </c>
       <c r="W82">
-        <v>0.1292690076606213</v>
+        <v>0.1294854396648112</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8179515667285063</v>
+        <v>0.807853399238031</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1396394319536088</v>
+        <v>0.1856695273913892</v>
       </c>
       <c r="C83">
-        <v>-243.9703830332508</v>
+        <v>-298.2602736357068</v>
       </c>
       <c r="D83">
-        <v>148.9778067634493</v>
+        <v>99.95023949181683</v>
       </c>
       <c r="E83">
-        <v>385.6158567143543</v>
+        <v>390.8781800451778</v>
       </c>
       <c r="F83">
-        <v>426.2481897967001</v>
+        <v>431.5105131275236</v>
       </c>
       <c r="G83">
         <v>33.3</v>
@@ -8093,45 +8093,45 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M83">
-        <v>62.57323426215558</v>
+        <v>86.64731103600674</v>
       </c>
       <c r="N83">
-        <v>-12.02323426215557</v>
+        <v>-36.09731103600673</v>
       </c>
       <c r="O83">
-        <v>-1.755392202274713</v>
+        <v>-5.270207411256982</v>
       </c>
       <c r="P83">
-        <v>-10.26784205988086</v>
+        <v>-30.82710362474975</v>
       </c>
       <c r="Q83">
-        <v>12.53215794011914</v>
+        <v>-8.027103624749746</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1829275043426938</v>
+        <v>0.194657340349401</v>
       </c>
       <c r="T83">
-        <v>3.166916959415561</v>
+        <v>3.437813864882239</v>
       </c>
       <c r="U83">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1179465962887525</v>
+        <v>0.08517633047992774</v>
       </c>
       <c r="W83">
-        <v>0.1294854396648112</v>
+        <v>0.1836965928396305</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.807853399238031</v>
+        <v>0.5833995238351216</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1856695273913892</v>
+        <v>0.1872195273913892</v>
       </c>
       <c r="C84">
-        <v>-298.2602736357068</v>
+        <v>-304.6180812611677</v>
       </c>
       <c r="D84">
-        <v>99.95023949181683</v>
+        <v>98.85475519717939</v>
       </c>
       <c r="E84">
-        <v>390.8781800451778</v>
+        <v>396.1405033760013</v>
       </c>
       <c r="F84">
-        <v>431.5105131275236</v>
+        <v>436.7728364583471</v>
       </c>
       <c r="G84">
         <v>33.3</v>
@@ -8175,37 +8175,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M84">
-        <v>86.64731103600674</v>
+        <v>87.70398556083609</v>
       </c>
       <c r="N84">
-        <v>-36.09731103600673</v>
+        <v>-37.15398556083608</v>
       </c>
       <c r="O84">
-        <v>-5.270207411256982</v>
+        <v>-5.424481891882067</v>
       </c>
       <c r="P84">
-        <v>-30.82710362474975</v>
+        <v>-31.72950366895401</v>
       </c>
       <c r="Q84">
-        <v>-8.027103624749746</v>
+        <v>-8.929503668954009</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.194657340349401</v>
+        <v>0.203413654487601</v>
       </c>
       <c r="T84">
-        <v>3.437813864882239</v>
+        <v>3.640038209875313</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.08517633047992774</v>
+        <v>0.08415010963077199</v>
       </c>
       <c r="W84">
-        <v>0.1836965928396305</v>
+        <v>0.183902657986141</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5833995238351216</v>
+        <v>0.5763706139093974</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1872195273913892</v>
+        <v>0.1887695273913892</v>
       </c>
       <c r="C85">
-        <v>-304.6180812611677</v>
+        <v>-310.9521355639777</v>
       </c>
       <c r="D85">
-        <v>98.85475519717939</v>
+        <v>97.78302422519288</v>
       </c>
       <c r="E85">
-        <v>396.1405033760013</v>
+        <v>401.4028267068247</v>
       </c>
       <c r="F85">
-        <v>436.7728364583471</v>
+        <v>442.0351597891705</v>
       </c>
       <c r="G85">
         <v>33.3</v>
@@ -8257,37 +8257,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M85">
-        <v>87.70398556083609</v>
+        <v>88.76066008566544</v>
       </c>
       <c r="N85">
-        <v>-37.15398556083608</v>
+        <v>-38.21066008566542</v>
       </c>
       <c r="O85">
-        <v>-5.424481891882067</v>
+        <v>-5.578756372507152</v>
       </c>
       <c r="P85">
-        <v>-31.72950366895401</v>
+        <v>-32.63190371315827</v>
       </c>
       <c r="Q85">
-        <v>-8.929503668954009</v>
+        <v>-9.831903713158272</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.203413654487601</v>
+        <v>0.2132645078930761</v>
       </c>
       <c r="T85">
-        <v>3.640038209875313</v>
+        <v>3.86754059799252</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.08415010963077199</v>
+        <v>0.08314832261135806</v>
       </c>
       <c r="W85">
-        <v>0.183902657986141</v>
+        <v>0.1841038168196393</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5763706139093974</v>
+        <v>0.5695090589819045</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1887695273913892</v>
+        <v>0.1903195273913892</v>
       </c>
       <c r="C86">
-        <v>-310.9521355639775</v>
+        <v>-317.2632008211331</v>
       </c>
       <c r="D86">
-        <v>97.78302422519288</v>
+        <v>96.73428229886078</v>
       </c>
       <c r="E86">
-        <v>401.4028267068247</v>
+        <v>406.6651500376481</v>
       </c>
       <c r="F86">
-        <v>442.0351597891705</v>
+        <v>447.2974831199939</v>
       </c>
       <c r="G86">
         <v>33.3</v>
@@ -8339,37 +8339,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M86">
-        <v>88.76066008566544</v>
+        <v>89.81733461049478</v>
       </c>
       <c r="N86">
-        <v>-38.21066008566542</v>
+        <v>-39.26733461049477</v>
       </c>
       <c r="O86">
-        <v>-5.578756372507152</v>
+        <v>-5.733030853132236</v>
       </c>
       <c r="P86">
-        <v>-32.63190371315827</v>
+        <v>-33.53430375736254</v>
       </c>
       <c r="Q86">
-        <v>-9.831903713158272</v>
+        <v>-10.73430375736254</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.213264507893076</v>
+        <v>0.2244288084192811</v>
       </c>
       <c r="T86">
-        <v>3.867540597992518</v>
+        <v>4.125376637858686</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.08314832261135806</v>
+        <v>0.08217010705122442</v>
       </c>
       <c r="W86">
-        <v>0.1841038168196393</v>
+        <v>0.1843002425041141</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5695090589819045</v>
+        <v>0.5628089524056468</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1903195273913892</v>
+        <v>0.1918695273913892</v>
       </c>
       <c r="C87">
-        <v>-317.2632008211331</v>
+        <v>-323.5520088694807</v>
       </c>
       <c r="D87">
-        <v>96.73428229886078</v>
+        <v>95.70779758133665</v>
       </c>
       <c r="E87">
-        <v>406.6651500376481</v>
+        <v>411.9274733684716</v>
       </c>
       <c r="F87">
-        <v>447.2974831199939</v>
+        <v>452.5598064508174</v>
       </c>
       <c r="G87">
         <v>33.3</v>
@@ -8421,37 +8421,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M87">
-        <v>89.81733461049478</v>
+        <v>90.87400913532414</v>
       </c>
       <c r="N87">
-        <v>-39.26733461049477</v>
+        <v>-40.32400913532413</v>
       </c>
       <c r="O87">
-        <v>-5.733030853132236</v>
+        <v>-5.887305333757323</v>
       </c>
       <c r="P87">
-        <v>-33.53430375736254</v>
+        <v>-34.43670380156681</v>
       </c>
       <c r="Q87">
-        <v>-10.73430375736254</v>
+        <v>-11.63670380156681</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2244288084192811</v>
+        <v>0.2371880090206583</v>
       </c>
       <c r="T87">
-        <v>4.125376637858686</v>
+        <v>4.420046397705735</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.08217010705122442</v>
+        <v>0.08121464069016367</v>
       </c>
       <c r="W87">
-        <v>0.1843002425041141</v>
+        <v>0.1844921001494151</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5628089524056468</v>
+        <v>0.556264662261395</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1918695273913892</v>
+        <v>0.1934195273913892</v>
       </c>
       <c r="C88">
-        <v>-323.5520088694807</v>
+        <v>-329.8192608088192</v>
       </c>
       <c r="D88">
-        <v>95.70779758133665</v>
+        <v>94.70286897282166</v>
       </c>
       <c r="E88">
-        <v>411.9274733684716</v>
+        <v>417.1897966992951</v>
       </c>
       <c r="F88">
-        <v>452.5598064508174</v>
+        <v>457.8221297816409</v>
       </c>
       <c r="G88">
         <v>33.3</v>
@@ -8503,37 +8503,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M88">
-        <v>90.87400913532414</v>
+        <v>91.93068366015349</v>
       </c>
       <c r="N88">
-        <v>-40.32400913532413</v>
+        <v>-41.38068366015348</v>
       </c>
       <c r="O88">
-        <v>-5.887305333757323</v>
+        <v>-6.041579814382407</v>
       </c>
       <c r="P88">
-        <v>-34.43670380156681</v>
+        <v>-35.33910384577107</v>
       </c>
       <c r="Q88">
-        <v>-11.63670380156681</v>
+        <v>-12.53910384577107</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2371880090206583</v>
+        <v>0.2519101635607089</v>
       </c>
       <c r="T88">
-        <v>4.420046397705735</v>
+        <v>4.760049966760022</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08121464069016367</v>
+        <v>0.08028113907303534</v>
       </c>
       <c r="W88">
-        <v>0.1844921001494151</v>
+        <v>0.1846795472741345</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.556264662261395</v>
+        <v>0.5498708155687353</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1934195273913892</v>
+        <v>0.1949695273913892</v>
       </c>
       <c r="C89">
-        <v>-329.8192608088192</v>
+        <v>-336.0656285988218</v>
       </c>
       <c r="D89">
-        <v>94.70286897282166</v>
+        <v>93.71882451364245</v>
       </c>
       <c r="E89">
-        <v>417.1897966992951</v>
+        <v>422.4521200301185</v>
       </c>
       <c r="F89">
-        <v>457.8221297816409</v>
+        <v>463.0844531124643</v>
       </c>
       <c r="G89">
         <v>33.3</v>
@@ -8585,37 +8585,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M89">
-        <v>91.93068366015349</v>
+        <v>92.98735818498284</v>
       </c>
       <c r="N89">
-        <v>-41.38068366015348</v>
+        <v>-42.43735818498283</v>
       </c>
       <c r="O89">
-        <v>-6.041579814382407</v>
+        <v>-6.195854295007492</v>
       </c>
       <c r="P89">
-        <v>-35.33910384577107</v>
+        <v>-36.24150388997533</v>
       </c>
       <c r="Q89">
-        <v>-12.53910384577107</v>
+        <v>-13.44150388997533</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2519101635607089</v>
+        <v>0.2690860105241014</v>
       </c>
       <c r="T89">
-        <v>4.760049966760022</v>
+        <v>5.156720797323358</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08028113907303534</v>
+        <v>0.07936885340175086</v>
       </c>
       <c r="W89">
-        <v>0.1846795472741345</v>
+        <v>0.1848627342369284</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5498708155687353</v>
+        <v>0.5436222835736361</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1949695273913892</v>
+        <v>0.1965195273913892</v>
       </c>
       <c r="C90">
-        <v>-336.0656285988218</v>
+        <v>-342.291756557422</v>
       </c>
       <c r="D90">
-        <v>93.71882451364245</v>
+        <v>92.75501988586575</v>
       </c>
       <c r="E90">
-        <v>422.4521200301185</v>
+        <v>427.714443360942</v>
       </c>
       <c r="F90">
-        <v>463.0844531124643</v>
+        <v>468.3467764432878</v>
       </c>
       <c r="G90">
         <v>33.3</v>
@@ -8667,37 +8667,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M90">
-        <v>92.98735818498284</v>
+        <v>94.04403270981219</v>
       </c>
       <c r="N90">
-        <v>-42.43735818498283</v>
+        <v>-43.49403270981217</v>
       </c>
       <c r="O90">
-        <v>-6.195854295007492</v>
+        <v>-6.350128775632577</v>
       </c>
       <c r="P90">
-        <v>-36.24150388997533</v>
+        <v>-37.1439039341796</v>
       </c>
       <c r="Q90">
-        <v>-13.44150388997533</v>
+        <v>-14.3439039341796</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2690860105241014</v>
+        <v>0.2893847387535651</v>
       </c>
       <c r="T90">
-        <v>5.156720797323358</v>
+        <v>5.625513597080027</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.07936885340175086</v>
+        <v>0.07847706853206828</v>
       </c>
       <c r="W90">
-        <v>0.1848627342369284</v>
+        <v>0.1850418046387607</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5436222835736361</v>
+        <v>0.5375141680278649</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1965195273913892</v>
+        <v>0.1980695273913892</v>
       </c>
       <c r="C91">
-        <v>-342.291756557422</v>
+        <v>-348.4982627676837</v>
       </c>
       <c r="D91">
-        <v>92.75501988586575</v>
+        <v>91.81083700642752</v>
       </c>
       <c r="E91">
-        <v>427.714443360942</v>
+        <v>432.9767666917655</v>
       </c>
       <c r="F91">
-        <v>468.3467764432878</v>
+        <v>473.6090997741113</v>
       </c>
       <c r="G91">
         <v>33.3</v>
@@ -8749,37 +8749,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M91">
-        <v>94.04403270981219</v>
+        <v>95.10070723464155</v>
       </c>
       <c r="N91">
-        <v>-43.49403270981217</v>
+        <v>-44.55070723464154</v>
       </c>
       <c r="O91">
-        <v>-6.350128775632577</v>
+        <v>-6.504403256257664</v>
       </c>
       <c r="P91">
-        <v>-37.1439039341796</v>
+        <v>-38.04630397838388</v>
       </c>
       <c r="Q91">
-        <v>-14.3439039341796</v>
+        <v>-15.24630397838387</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2893847387535651</v>
+        <v>0.3137432126289217</v>
       </c>
       <c r="T91">
-        <v>5.625513597080027</v>
+        <v>6.18806495678803</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.07847706853206828</v>
+        <v>0.07760510110393418</v>
       </c>
       <c r="W91">
-        <v>0.1850418046387607</v>
+        <v>0.18521689569833</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5375141680278649</v>
+        <v>0.5315417883831108</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1980695273913892</v>
+        <v>0.1996195273913892</v>
       </c>
       <c r="C92">
-        <v>-348.4982627676837</v>
+        <v>-354.6857403996114</v>
       </c>
       <c r="D92">
-        <v>91.81083700642752</v>
+        <v>90.8856827053233</v>
       </c>
       <c r="E92">
-        <v>432.9767666917655</v>
+        <v>438.2390900225889</v>
       </c>
       <c r="F92">
-        <v>473.6090997741113</v>
+        <v>478.8714231049347</v>
       </c>
       <c r="G92">
         <v>33.3</v>
@@ -8831,37 +8831,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M92">
-        <v>95.10070723464155</v>
+        <v>96.15738175947089</v>
       </c>
       <c r="N92">
-        <v>-44.55070723464154</v>
+        <v>-45.60738175947088</v>
       </c>
       <c r="O92">
-        <v>-6.504403256257664</v>
+        <v>-6.658677736882749</v>
       </c>
       <c r="P92">
-        <v>-38.04630397838388</v>
+        <v>-38.94870402258813</v>
       </c>
       <c r="Q92">
-        <v>-15.24630397838387</v>
+        <v>-16.14870402258813</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3137432126289217</v>
+        <v>0.3435146806988019</v>
       </c>
       <c r="T92">
-        <v>6.18806495678803</v>
+        <v>6.875627729764479</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.07760510110393418</v>
+        <v>0.07675229779509973</v>
       </c>
       <c r="W92">
-        <v>0.18521689569833</v>
+        <v>0.185388138602744</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5315417883831108</v>
+        <v>0.5257006698294502</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1996195273913892</v>
+        <v>0.2011695273913892</v>
       </c>
       <c r="C93">
-        <v>-354.6857403996114</v>
+        <v>-360.8547589528408</v>
       </c>
       <c r="D93">
-        <v>90.8856827053233</v>
+        <v>89.97898748291732</v>
       </c>
       <c r="E93">
-        <v>438.2390900225889</v>
+        <v>443.5014133534124</v>
       </c>
       <c r="F93">
-        <v>478.8714231049347</v>
+        <v>484.1337464357582</v>
       </c>
       <c r="G93">
         <v>33.3</v>
@@ -8913,37 +8913,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M93">
-        <v>96.15738175947089</v>
+        <v>97.21405628430024</v>
       </c>
       <c r="N93">
-        <v>-45.60738175947088</v>
+        <v>-46.66405628430023</v>
       </c>
       <c r="O93">
-        <v>-6.658677736882749</v>
+        <v>-6.812952217507833</v>
       </c>
       <c r="P93">
-        <v>-38.94870402258813</v>
+        <v>-39.8511040667924</v>
       </c>
       <c r="Q93">
-        <v>-16.14870402258813</v>
+        <v>-17.05110406679239</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3435146806988019</v>
+        <v>0.3807290157861523</v>
       </c>
       <c r="T93">
-        <v>6.875627729764479</v>
+        <v>7.735081195985041</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.07675229779509973</v>
+        <v>0.07591803368863126</v>
       </c>
       <c r="W93">
-        <v>0.185388138602744</v>
+        <v>0.1855556588353229</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5257006698294502</v>
+        <v>0.5199865321139128</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2011695273913892</v>
+        <v>0.2027195273913892</v>
       </c>
       <c r="C94">
-        <v>-360.8547589528408</v>
+        <v>-367.0058654256799</v>
       </c>
       <c r="D94">
-        <v>89.97898748291732</v>
+        <v>89.09020434090171</v>
       </c>
       <c r="E94">
-        <v>443.5014133534124</v>
+        <v>448.7637366842358</v>
       </c>
       <c r="F94">
-        <v>484.1337464357582</v>
+        <v>489.3960697665816</v>
       </c>
       <c r="G94">
         <v>33.3</v>
@@ -8995,37 +8995,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M94">
-        <v>97.21405628430024</v>
+        <v>98.27073080912959</v>
       </c>
       <c r="N94">
-        <v>-46.66405628430023</v>
+        <v>-47.72073080912958</v>
       </c>
       <c r="O94">
-        <v>-6.812952217507833</v>
+        <v>-6.967226698132918</v>
       </c>
       <c r="P94">
-        <v>-39.8511040667924</v>
+        <v>-40.75350411099666</v>
       </c>
       <c r="Q94">
-        <v>-17.05110406679239</v>
+        <v>-17.95350411099666</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3807290157861523</v>
+        <v>0.4285760180413169</v>
       </c>
       <c r="T94">
-        <v>7.735081195985041</v>
+        <v>8.840092795411476</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.07591803368863126</v>
+        <v>0.07510171074574275</v>
       </c>
       <c r="W94">
-        <v>0.1855556588353229</v>
+        <v>0.1857195764822548</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5199865321139128</v>
+        <v>0.5143952790804298</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2027195273913892</v>
+        <v>0.2042695273913892</v>
       </c>
       <c r="C95">
-        <v>-367.0058654256799</v>
+        <v>-373.1395854155427</v>
       </c>
       <c r="D95">
-        <v>89.09020434090171</v>
+        <v>88.2188076818624</v>
       </c>
       <c r="E95">
-        <v>448.7637366842358</v>
+        <v>454.0260600150593</v>
       </c>
       <c r="F95">
-        <v>489.3960697665816</v>
+        <v>494.6583930974051</v>
       </c>
       <c r="G95">
         <v>33.3</v>
@@ -9077,37 +9077,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M95">
-        <v>98.27073080912959</v>
+        <v>99.32740533395895</v>
       </c>
       <c r="N95">
-        <v>-47.72073080912958</v>
+        <v>-48.77740533395894</v>
       </c>
       <c r="O95">
-        <v>-6.967226698132918</v>
+        <v>-7.121501178758004</v>
       </c>
       <c r="P95">
-        <v>-40.75350411099666</v>
+        <v>-41.65590415520094</v>
       </c>
       <c r="Q95">
-        <v>-17.95350411099666</v>
+        <v>-18.85590415520094</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4285760180413169</v>
+        <v>0.4923720210482032</v>
       </c>
       <c r="T95">
-        <v>8.840092795411476</v>
+        <v>10.31344159464673</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.07510171074574275</v>
+        <v>0.07430275637610718</v>
       </c>
       <c r="W95">
-        <v>0.1857195764822548</v>
+        <v>0.1858800065196777</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5143952790804298</v>
+        <v>0.5089229888774465</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2042695273913892</v>
+        <v>0.2058195273913892</v>
       </c>
       <c r="C96">
-        <v>-373.1395854155427</v>
+        <v>-379.256424155429</v>
       </c>
       <c r="D96">
-        <v>88.2188076818624</v>
+        <v>87.36429227279959</v>
       </c>
       <c r="E96">
-        <v>454.0260600150593</v>
+        <v>459.2883833458828</v>
       </c>
       <c r="F96">
-        <v>494.6583930974051</v>
+        <v>499.9207164282286</v>
       </c>
       <c r="G96">
         <v>33.3</v>
@@ -9159,37 +9159,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M96">
-        <v>99.32740533395895</v>
+        <v>100.3840798587883</v>
       </c>
       <c r="N96">
-        <v>-48.77740533395894</v>
+        <v>-49.83407985878829</v>
       </c>
       <c r="O96">
-        <v>-7.121501178758004</v>
+        <v>-7.275775659383089</v>
       </c>
       <c r="P96">
-        <v>-41.65590415520094</v>
+        <v>-42.5583041994052</v>
       </c>
       <c r="Q96">
-        <v>-18.85590415520094</v>
+        <v>-19.7583041994052</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4923720210482032</v>
+        <v>0.5816864252578441</v>
       </c>
       <c r="T96">
-        <v>10.31344159464673</v>
+        <v>12.37612991357608</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.07430275637610718</v>
+        <v>0.07352062209846397</v>
       </c>
       <c r="W96">
-        <v>0.1858800065196777</v>
+        <v>0.1860370590826284</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5089229888774465</v>
+        <v>0.5035659047839998</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2058195273913892</v>
+        <v>0.2412681648398951</v>
       </c>
       <c r="C97">
-        <v>-379.256424155429</v>
+        <v>-400.3624789975215</v>
       </c>
       <c r="D97">
-        <v>87.36429227279959</v>
+        <v>71.52056076153052</v>
       </c>
       <c r="E97">
-        <v>459.2883833458828</v>
+        <v>464.5507066767062</v>
       </c>
       <c r="F97">
-        <v>499.9207164282286</v>
+        <v>505.183039759052</v>
       </c>
       <c r="G97">
         <v>33.3</v>
@@ -9241,45 +9241,45 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M97">
-        <v>100.3840798587883</v>
+        <v>119.1221607751845</v>
       </c>
       <c r="N97">
-        <v>-49.83407985878829</v>
+        <v>-68.57216077518446</v>
       </c>
       <c r="O97">
-        <v>-7.275775659383089</v>
+        <v>-10.01153547317693</v>
       </c>
       <c r="P97">
-        <v>-42.5583041994052</v>
+        <v>-58.56062530200752</v>
       </c>
       <c r="Q97">
-        <v>-19.7583041994052</v>
+        <v>-35.76062530200753</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5816864252578441</v>
+        <v>0.7231239677849531</v>
       </c>
       <c r="T97">
-        <v>12.37612991357608</v>
+        <v>15.64258586108437</v>
       </c>
       <c r="U97">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07352062209846397</v>
+        <v>0.06195572639022735</v>
       </c>
       <c r="W97">
-        <v>0.1860370590826284</v>
+        <v>0.2211908397171844</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.5035659047839998</v>
+        <v>0.4243542903440229</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2412681648398951</v>
+        <v>0.2431681648398951</v>
       </c>
       <c r="C98">
-        <v>-400.3624789975214</v>
+        <v>-406.3133078203888</v>
       </c>
       <c r="D98">
-        <v>71.52056076153052</v>
+        <v>70.83205526948656</v>
       </c>
       <c r="E98">
-        <v>464.5507066767062</v>
+        <v>469.8130300075296</v>
       </c>
       <c r="F98">
-        <v>505.183039759052</v>
+        <v>510.4453630898754</v>
       </c>
       <c r="G98">
         <v>33.3</v>
@@ -9323,37 +9323,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M98">
-        <v>119.1221607751845</v>
+        <v>120.3630166165926</v>
       </c>
       <c r="N98">
-        <v>-68.57216077518444</v>
+        <v>-69.81301661659262</v>
       </c>
       <c r="O98">
-        <v>-10.01153547317693</v>
+        <v>-10.19270042602252</v>
       </c>
       <c r="P98">
-        <v>-58.56062530200752</v>
+        <v>-59.62031619057009</v>
       </c>
       <c r="Q98">
-        <v>-35.76062530200751</v>
+        <v>-36.8203161905701</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7231239677849514</v>
+        <v>0.9488986237132685</v>
       </c>
       <c r="T98">
-        <v>15.64258586108433</v>
+        <v>20.85678114811244</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06195572639022735</v>
+        <v>0.06131700756146212</v>
       </c>
       <c r="W98">
-        <v>0.2211908397171844</v>
+        <v>0.2213414496170072</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4243542903440229</v>
+        <v>0.419979503845631</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2431681648398951</v>
+        <v>0.2450681648398951</v>
       </c>
       <c r="C99">
-        <v>-406.3133078203888</v>
+        <v>-412.2510069952171</v>
       </c>
       <c r="D99">
-        <v>70.83205526948656</v>
+        <v>70.15667942548181</v>
       </c>
       <c r="E99">
-        <v>469.8130300075296</v>
+        <v>475.0753533383531</v>
       </c>
       <c r="F99">
-        <v>510.4453630898754</v>
+        <v>515.7076864206989</v>
       </c>
       <c r="G99">
         <v>33.3</v>
@@ -9405,37 +9405,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M99">
-        <v>120.3630166165926</v>
+        <v>121.6038724580008</v>
       </c>
       <c r="N99">
-        <v>-69.81301661659262</v>
+        <v>-71.0538724580008</v>
       </c>
       <c r="O99">
-        <v>-10.19270042602252</v>
+        <v>-10.37386537886812</v>
       </c>
       <c r="P99">
-        <v>-59.62031619057009</v>
+        <v>-60.68000707913268</v>
       </c>
       <c r="Q99">
-        <v>-36.8203161905701</v>
+        <v>-37.88000707913268</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9488986237132685</v>
+        <v>1.400447935569903</v>
       </c>
       <c r="T99">
-        <v>20.85678114811244</v>
+        <v>31.28517172216866</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06131700756146212</v>
+        <v>0.06069132381083495</v>
       </c>
       <c r="W99">
-        <v>0.2213414496170072</v>
+        <v>0.2214889858454051</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.419979503845631</v>
+        <v>0.415693998704349</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2450681648398951</v>
+        <v>0.2469681648398951</v>
       </c>
       <c r="C100">
-        <v>-412.2510069952171</v>
+        <v>-418.1759485440597</v>
       </c>
       <c r="D100">
-        <v>70.15667942548181</v>
+        <v>69.49406120746258</v>
       </c>
       <c r="E100">
-        <v>475.0753533383531</v>
+        <v>480.3376766691765</v>
       </c>
       <c r="F100">
-        <v>515.7076864206989</v>
+        <v>520.9700097515223</v>
       </c>
       <c r="G100">
         <v>33.3</v>
@@ -9487,37 +9487,37 @@
         <v>50.55000000000001</v>
       </c>
       <c r="M100">
-        <v>121.6038724580008</v>
+        <v>122.844728299409</v>
       </c>
       <c r="N100">
-        <v>-71.0538724580008</v>
+        <v>-72.29472829940894</v>
       </c>
       <c r="O100">
-        <v>-10.37386537886812</v>
+        <v>-10.55503033171371</v>
       </c>
       <c r="P100">
-        <v>-60.68000707913268</v>
+        <v>-61.73969796769524</v>
       </c>
       <c r="Q100">
-        <v>-37.88000707913268</v>
+        <v>-38.93969796769524</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.400447935569903</v>
+        <v>2.755095871139805</v>
       </c>
       <c r="T100">
-        <v>31.28517172216866</v>
+        <v>62.57034344433731</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06069132381083495</v>
+        <v>0.06007828013597805</v>
       </c>
       <c r="W100">
-        <v>0.2214889858454051</v>
+        <v>0.2216335415439364</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.415693998704349</v>
+        <v>0.4114950694245072</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2469681648398951</v>
-      </c>
-      <c r="C101">
-        <v>-418.1759485440597</v>
-      </c>
-      <c r="D101">
-        <v>69.49406120746258</v>
-      </c>
-      <c r="E101">
-        <v>480.3376766691765</v>
-      </c>
-      <c r="F101">
-        <v>520.9700097515223</v>
-      </c>
-      <c r="G101">
-        <v>33.3</v>
-      </c>
-      <c r="H101">
-        <v>485.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>73.35000000000001</v>
-      </c>
-      <c r="K101">
-        <v>22.8</v>
-      </c>
-      <c r="L101">
-        <v>50.55000000000001</v>
-      </c>
-      <c r="M101">
-        <v>122.844728299409</v>
-      </c>
-      <c r="N101">
-        <v>-72.29472829940894</v>
-      </c>
-      <c r="O101">
-        <v>-10.55503033171371</v>
-      </c>
-      <c r="P101">
-        <v>-61.73969796769524</v>
-      </c>
-      <c r="Q101">
-        <v>-38.93969796769524</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.755095871139805</v>
-      </c>
-      <c r="T101">
-        <v>62.57034344433731</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06007828013597805</v>
-      </c>
-      <c r="W101">
-        <v>0.2216335415439364</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4114950694245072</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
